--- a/Dashboard_Backend.xlsx
+++ b/Dashboard_Backend.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMUL\Desktop\TOP outlets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A91384-0C7C-49DF-8C8F-446B2FED4A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AB46C8-94C4-492F-B98B-82C9B539BE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="571" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard Backend" sheetId="1" r:id="rId1"/>
@@ -397,10 +397,12 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -869,52 +871,52 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>2002095</v>
+        <v>2018993</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C2" s="9">
-        <v>200205300429</v>
+        <v>201613300337</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2" s="3">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="H2" s="3">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I2" s="7">
-        <v>24</v>
+        <v>35.333333333333343</v>
       </c>
       <c r="J2" s="7">
-        <v>26</v>
+        <v>25.333333333333339</v>
       </c>
       <c r="K2" s="4">
-        <v>41.613610000000001</v>
+        <v>106.73451</v>
       </c>
       <c r="L2" s="4">
-        <v>64.495710000000003</v>
+        <v>76.190640000000002</v>
       </c>
       <c r="M2" s="4">
-        <v>45.956506666666677</v>
+        <v>67.08329333333333</v>
       </c>
       <c r="N2" s="4">
-        <v>-9.3479019999999906</v>
+        <v>4.3093119999999914</v>
       </c>
       <c r="O2" s="5">
         <v>0</v>
       </c>
       <c r="P2" s="5">
-        <v>0.64495710000000006</v>
+        <v>0.38095319999999999</v>
       </c>
       <c r="Q2" s="6">
         <v>250</v>
@@ -923,106 +925,106 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>2002057</v>
+        <v>2009842</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C3" s="9">
-        <v>200205700151</v>
+        <v>200984201066</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3">
+        <v>15</v>
+      </c>
+      <c r="I3" s="7">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3">
-        <v>11</v>
-      </c>
-      <c r="H3" s="3">
-        <v>6</v>
-      </c>
-      <c r="I3" s="7">
-        <v>19.666666666666671</v>
-      </c>
       <c r="J3" s="7">
-        <v>33.666666666666671</v>
+        <v>26</v>
       </c>
       <c r="K3" s="4">
-        <v>30.21284</v>
+        <v>8.0576299999999996</v>
       </c>
       <c r="L3" s="4">
-        <v>21.680890000000002</v>
+        <v>35.567520000000002</v>
       </c>
       <c r="M3" s="4">
-        <v>27.61830333333333</v>
+        <v>11.26651333333333</v>
       </c>
       <c r="N3" s="4">
-        <v>11.461073999999989</v>
+        <v>-22.047704</v>
       </c>
       <c r="O3" s="5">
         <v>0</v>
       </c>
       <c r="P3" s="5">
-        <v>0</v>
+        <v>0.35567520000000002</v>
       </c>
       <c r="Q3" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R3" s="8"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>2002057</v>
+        <v>2002095</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" s="9">
-        <v>200205700384</v>
+        <v>200209501162</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G4" s="3">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="H4" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I4" s="7">
-        <v>19.666666666666671</v>
+        <v>22.666666666666671</v>
       </c>
       <c r="J4" s="7">
         <v>31.666666666666671</v>
       </c>
       <c r="K4" s="4">
-        <v>24.68084</v>
+        <v>17.68657</v>
       </c>
       <c r="L4" s="4">
-        <v>28.490580000000001</v>
+        <v>103.1444</v>
       </c>
       <c r="M4" s="4">
-        <v>25.18221333333333</v>
+        <v>66.654969999999992</v>
       </c>
       <c r="N4" s="4">
-        <v>1.728075999999994</v>
+        <v>-23.158436000000009</v>
       </c>
       <c r="O4" s="5">
         <v>0</v>
       </c>
       <c r="P4" s="5">
-        <v>0.14245289999999999</v>
+        <v>1.031444</v>
       </c>
       <c r="Q4" s="6">
         <v>250</v>
@@ -1031,46 +1033,46 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>2011731</v>
+        <v>2022939</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="9">
+        <v>201327000332</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3">
+        <v>47</v>
+      </c>
+      <c r="G5" s="3">
         <v>24</v>
       </c>
-      <c r="C5" s="9">
-        <v>200205700568</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="3">
-        <v>38</v>
-      </c>
-      <c r="G5" s="3">
-        <v>42</v>
-      </c>
       <c r="H5" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I5" s="7">
-        <v>48</v>
+        <v>43.333333333333343</v>
       </c>
       <c r="J5" s="7">
-        <v>36</v>
+        <v>50.333333333333343</v>
       </c>
       <c r="K5" s="4">
-        <v>75.357900000000001</v>
+        <v>66.997240000000005</v>
       </c>
       <c r="L5" s="4">
-        <v>105.13197</v>
+        <v>24.459119999999999</v>
       </c>
       <c r="M5" s="4">
-        <v>130.32283666666669</v>
+        <v>34.158923333333327</v>
       </c>
       <c r="N5" s="4">
-        <v>51.255434000000037</v>
+        <v>16.531587999999989</v>
       </c>
       <c r="O5" s="5">
         <v>0</v>
@@ -1085,55 +1087,55 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>2002057</v>
+        <v>2023177</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="9">
+        <v>202317700011</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3">
         <v>20</v>
       </c>
-      <c r="C6" s="9">
-        <v>200205700596</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3">
-        <v>30</v>
-      </c>
       <c r="G6" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H6" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>30.666666666666671</v>
+        <v>18</v>
       </c>
       <c r="J6" s="7">
-        <v>42.666666666666671</v>
+        <v>28</v>
       </c>
       <c r="K6" s="4">
-        <v>40.000500000000002</v>
+        <v>33.348080000000003</v>
       </c>
       <c r="L6" s="4">
-        <v>33.733159999999998</v>
+        <v>20.83699</v>
       </c>
       <c r="M6" s="4">
-        <v>23.482389999999999</v>
+        <v>24.544803333333331</v>
       </c>
       <c r="N6" s="4">
-        <v>-5.5542920000000002</v>
+        <v>8.6167739999999959</v>
       </c>
       <c r="O6" s="5">
         <v>0</v>
       </c>
       <c r="P6" s="5">
-        <v>0.33733160000000001</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R6" s="8"/>
     </row>
@@ -1145,316 +1147,316 @@
         <v>20</v>
       </c>
       <c r="C7" s="9">
-        <v>200205700618</v>
+        <v>200205700596</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G7" s="3">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>6</v>
+        <v>30.666666666666671</v>
       </c>
       <c r="J7" s="7">
-        <v>6</v>
+        <v>42.666666666666671</v>
       </c>
       <c r="K7" s="4">
-        <v>0</v>
+        <v>40.000500000000002</v>
       </c>
       <c r="L7" s="4">
-        <v>45.891080000000002</v>
+        <v>33.733159999999998</v>
       </c>
       <c r="M7" s="4">
-        <v>4.365593333333333</v>
+        <v>23.482389999999999</v>
       </c>
       <c r="N7" s="4">
-        <v>-40.652368000000003</v>
+        <v>-5.5542920000000002</v>
       </c>
       <c r="O7" s="5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P7" s="5">
-        <v>0.45891080000000001</v>
+        <v>0.33733160000000001</v>
       </c>
       <c r="Q7" s="6">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="R7" s="8"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>2002060</v>
+        <v>2018993</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C8" s="9">
-        <v>200206000005</v>
+        <v>201178500076</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="3">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3">
+        <v>72</v>
+      </c>
+      <c r="H8" s="3">
+        <v>49</v>
+      </c>
+      <c r="I8" s="7">
+        <v>62</v>
+      </c>
+      <c r="J8" s="7">
         <v>33</v>
       </c>
-      <c r="H8" s="3">
-        <v>27</v>
-      </c>
-      <c r="I8" s="7">
-        <v>14.33333333333333</v>
-      </c>
-      <c r="J8" s="7">
-        <v>7.3333333333333286</v>
-      </c>
       <c r="K8" s="4">
-        <v>61.049709999999997</v>
+        <v>233.78666000000001</v>
       </c>
       <c r="L8" s="4">
-        <v>146.54689999999999</v>
+        <v>251.11296999999999</v>
       </c>
       <c r="M8" s="4">
-        <v>71.792686666666668</v>
+        <v>211.11028333333331</v>
       </c>
       <c r="N8" s="4">
-        <v>-60.395675999999987</v>
+        <v>2.219369999999941</v>
       </c>
       <c r="O8" s="5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P8" s="5">
-        <v>1.4654689999999999</v>
+        <v>1.883347275</v>
       </c>
       <c r="Q8" s="6">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="R8" s="8"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>2002060</v>
+        <v>2023303</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="C9" s="9">
-        <v>200206000006</v>
+        <v>201330600340</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F9" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G9" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I9" s="7">
-        <v>16.333333333333329</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="J9" s="7">
-        <v>16.333333333333329</v>
+        <v>16.666666666666671</v>
       </c>
       <c r="K9" s="4">
-        <v>41.232799999999997</v>
+        <v>83.232339999999994</v>
       </c>
       <c r="L9" s="4">
-        <v>65.255870000000002</v>
+        <v>57.942810000000001</v>
       </c>
       <c r="M9" s="4">
-        <v>45.289326666666661</v>
+        <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-10.908678000000011</v>
+        <v>-57.942810000000001</v>
       </c>
       <c r="O9" s="5">
         <v>0</v>
       </c>
       <c r="P9" s="5">
-        <v>0.65255870000000005</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R9" s="8"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>2002060</v>
+        <v>2022679</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C10" s="9">
-        <v>200206000020</v>
+        <v>201294400165</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H10" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I10" s="7">
-        <v>36.333333333333343</v>
+        <v>46</v>
       </c>
       <c r="J10" s="7">
-        <v>34.333333333333343</v>
+        <v>42</v>
       </c>
       <c r="K10" s="4">
-        <v>302.35682000000003</v>
+        <v>99.850290000000001</v>
       </c>
       <c r="L10" s="4">
-        <v>568.03162999999995</v>
+        <v>81.764769999999999</v>
       </c>
       <c r="M10" s="4">
-        <v>476.47446999999988</v>
+        <v>83.753239999999991</v>
       </c>
       <c r="N10" s="4">
-        <v>3.7377339999999322</v>
+        <v>18.739117999999991</v>
       </c>
       <c r="O10" s="5">
         <v>0</v>
       </c>
       <c r="P10" s="5">
-        <v>4.2602372249999991</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>2002060</v>
+        <v>2022679</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C11" s="9">
-        <v>200206000044</v>
+        <v>201294400288</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3">
+        <v>55</v>
+      </c>
+      <c r="G11" s="3">
+        <v>43</v>
+      </c>
+      <c r="H11" s="3">
         <v>25</v>
       </c>
-      <c r="G11" s="3">
-        <v>21</v>
-      </c>
-      <c r="H11" s="3">
-        <v>20</v>
-      </c>
       <c r="I11" s="7">
-        <v>24.666666666666671</v>
+        <v>50.333333333333343</v>
       </c>
       <c r="J11" s="7">
-        <v>24.666666666666671</v>
+        <v>45.333333333333343</v>
       </c>
       <c r="K11" s="4">
-        <v>131.09913</v>
+        <v>92.417149999999992</v>
       </c>
       <c r="L11" s="4">
-        <v>79.851129999999998</v>
+        <v>66.352029999999999</v>
       </c>
       <c r="M11" s="4">
-        <v>94.131806666666662</v>
+        <v>59.695973333333328</v>
       </c>
       <c r="N11" s="4">
-        <v>33.107037999999989</v>
+        <v>5.2831379999999939</v>
       </c>
       <c r="O11" s="5">
         <v>0</v>
       </c>
       <c r="P11" s="5">
-        <v>0</v>
+        <v>0.33176014999999998</v>
       </c>
       <c r="Q11" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R11" s="8"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>2002060</v>
+        <v>2022679</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C12" s="9">
-        <v>200206000046</v>
+        <v>201294400279</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F12" s="3">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G12" s="3">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="H12" s="3">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I12" s="7">
-        <v>37</v>
+        <v>45.333333333333343</v>
       </c>
       <c r="J12" s="7">
-        <v>34</v>
+        <v>23.333333333333339</v>
       </c>
       <c r="K12" s="4">
-        <v>191.05100999999999</v>
+        <v>72.272829999999999</v>
       </c>
       <c r="L12" s="4">
-        <v>240.58680000000001</v>
+        <v>111.96988</v>
       </c>
       <c r="M12" s="4">
-        <v>215.37703666666661</v>
+        <v>83.111879999999999</v>
       </c>
       <c r="N12" s="4">
-        <v>17.865643999999921</v>
+        <v>-12.235624</v>
       </c>
       <c r="O12" s="5">
         <v>0</v>
       </c>
       <c r="P12" s="5">
-        <v>1.2029339999999999</v>
+        <v>1.1196988000000001</v>
       </c>
       <c r="Q12" s="6">
         <v>250</v>
@@ -1463,106 +1465,106 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>2002060</v>
+        <v>2023303</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="C13" s="9">
-        <v>200206000047</v>
+        <v>201624800522</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F13" s="3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G13" s="3">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H13" s="3">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I13" s="7">
-        <v>14.66666666666667</v>
+        <v>16.666666666666671</v>
       </c>
       <c r="J13" s="7">
-        <v>21.666666666666671</v>
+        <v>0.6666666666666714</v>
       </c>
       <c r="K13" s="4">
-        <v>132.00389999999999</v>
+        <v>26.563960000000002</v>
       </c>
       <c r="L13" s="4">
-        <v>176.67819</v>
+        <v>127.87345000000001</v>
       </c>
       <c r="M13" s="4">
-        <v>162.89900333333341</v>
+        <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>18.800614000000081</v>
+        <v>-127.87345000000001</v>
       </c>
       <c r="O13" s="5">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="P13" s="5">
         <v>0</v>
       </c>
       <c r="Q13" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R13" s="8"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>2002060</v>
+        <v>2023177</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="C14" s="9">
-        <v>200206000084</v>
+        <v>202317700022</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F14" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G14" s="3">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>35.666666666666657</v>
+        <v>22</v>
       </c>
       <c r="J14" s="7">
-        <v>30.666666666666661</v>
+        <v>31</v>
       </c>
       <c r="K14" s="4">
-        <v>109.97247</v>
+        <v>36.343389999999999</v>
       </c>
       <c r="L14" s="4">
-        <v>194.62161</v>
+        <v>28.312449999999998</v>
       </c>
       <c r="M14" s="4">
-        <v>137.57176666666669</v>
+        <v>24.969480000000001</v>
       </c>
       <c r="N14" s="4">
-        <v>-29.535489999999982</v>
+        <v>1.6509260000000019</v>
       </c>
       <c r="O14" s="5">
         <v>0</v>
       </c>
       <c r="P14" s="5">
-        <v>1.9462161</v>
+        <v>0.14156225</v>
       </c>
       <c r="Q14" s="6">
         <v>250</v>
@@ -1625,52 +1627,52 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>2002060</v>
+        <v>2023177</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="C16" s="9">
-        <v>200206000101</v>
+        <v>202317700044</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F16" s="3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G16" s="3">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H16" s="3">
+        <v>19</v>
+      </c>
+      <c r="I16" s="7">
+        <v>25</v>
+      </c>
+      <c r="J16" s="7">
         <v>26</v>
       </c>
-      <c r="I16" s="7">
-        <v>24.666666666666671</v>
-      </c>
-      <c r="J16" s="7">
-        <v>18.666666666666671</v>
-      </c>
       <c r="K16" s="4">
-        <v>47.029890000000002</v>
+        <v>44.575009999999999</v>
       </c>
       <c r="L16" s="4">
-        <v>132.23799</v>
+        <v>65.395139999999998</v>
       </c>
       <c r="M16" s="4">
-        <v>92.999686666666662</v>
+        <v>48.297863333333332</v>
       </c>
       <c r="N16" s="4">
-        <v>-20.638366000000001</v>
+        <v>-7.4377040000000036</v>
       </c>
       <c r="O16" s="5">
         <v>0</v>
       </c>
       <c r="P16" s="5">
-        <v>1.3223799000000001</v>
+        <v>0.65395139999999996</v>
       </c>
       <c r="Q16" s="6">
         <v>250</v>
@@ -1679,214 +1681,214 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>2018993</v>
+        <v>2022639</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C17" s="9">
-        <v>200206700008</v>
+        <v>200207300363</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F17" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G17" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H17" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>15.66666666666667</v>
+        <v>26.666666666666671</v>
       </c>
       <c r="J17" s="7">
-        <v>24.666666666666671</v>
+        <v>38.666666666666671</v>
       </c>
       <c r="K17" s="4">
-        <v>30.629629999999999</v>
+        <v>82.051349999999999</v>
       </c>
       <c r="L17" s="4">
-        <v>52.049349999999997</v>
+        <v>33.738280000000003</v>
       </c>
       <c r="M17" s="4">
-        <v>43.834753333333332</v>
+        <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>0.55235399999999402</v>
+        <v>-33.738280000000003</v>
       </c>
       <c r="O17" s="5">
         <v>0</v>
       </c>
       <c r="P17" s="5">
-        <v>0.39037012500000001</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R17" s="8"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>2022939</v>
+        <v>2002060</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C18" s="9">
-        <v>200206700482</v>
+        <v>200206000005</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F18" s="3">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="G18" s="3">
         <v>33</v>
       </c>
       <c r="H18" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I18" s="7">
-        <v>50.666666666666657</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="J18" s="7">
-        <v>44.666666666666657</v>
+        <v>7.3333333333333286</v>
       </c>
       <c r="K18" s="4">
-        <v>132.01094000000001</v>
+        <v>61.049709999999997</v>
       </c>
       <c r="L18" s="4">
-        <v>117.13229</v>
+        <v>146.54689999999999</v>
       </c>
       <c r="M18" s="4">
-        <v>124.99812666666671</v>
+        <v>71.792686666666668</v>
       </c>
       <c r="N18" s="4">
-        <v>32.865462000000051</v>
+        <v>-60.395675999999987</v>
       </c>
       <c r="O18" s="5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P18" s="5">
-        <v>0</v>
+        <v>1.4654689999999999</v>
       </c>
       <c r="Q18" s="6">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="R18" s="8"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>2022939</v>
+        <v>2021330</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="C19" s="9">
-        <v>200206700519</v>
+        <v>202133000511</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F19" s="3">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="G19" s="3">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="H19" s="3">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I19" s="7">
-        <v>40.666666666666657</v>
+        <v>16.333333333333329</v>
       </c>
       <c r="J19" s="7">
-        <v>17.666666666666661</v>
+        <v>2.333333333333329</v>
       </c>
       <c r="K19" s="4">
-        <v>56.670520000000003</v>
+        <v>3.39411</v>
       </c>
       <c r="L19" s="4">
-        <v>110.0772</v>
+        <v>123.17138</v>
       </c>
       <c r="M19" s="4">
-        <v>62.187460000000009</v>
+        <v>36.303743333333337</v>
       </c>
       <c r="N19" s="4">
-        <v>-35.452247999999997</v>
+        <v>-79.606887999999998</v>
       </c>
       <c r="O19" s="5">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="P19" s="5">
-        <v>1.1007720000000001</v>
+        <v>1.2317138000000001</v>
       </c>
       <c r="Q19" s="6">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="R19" s="8"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>2002070</v>
+        <v>2018993</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C20" s="9">
-        <v>200207000230</v>
+        <v>200206700008</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G20" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I20" s="7">
-        <v>11</v>
+        <v>15.66666666666667</v>
       </c>
       <c r="J20" s="7">
-        <v>11</v>
+        <v>24.666666666666671</v>
       </c>
       <c r="K20" s="4">
-        <v>0</v>
+        <v>30.629629999999999</v>
       </c>
       <c r="L20" s="4">
-        <v>782.71015</v>
+        <v>52.049349999999997</v>
       </c>
       <c r="M20" s="4">
-        <v>283.22349333333341</v>
+        <v>43.834753333333332</v>
       </c>
       <c r="N20" s="4">
-        <v>-442.84195799999992</v>
+        <v>0.55235399999999402</v>
       </c>
       <c r="O20" s="5">
         <v>0</v>
       </c>
       <c r="P20" s="5">
-        <v>7.8271015000000004</v>
+        <v>0.39037012500000001</v>
       </c>
       <c r="Q20" s="6">
         <v>250</v>
@@ -1895,52 +1897,52 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>2002070</v>
+        <v>2023085</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C21" s="9">
-        <v>200207001063</v>
+        <v>200405300624</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="F21" s="3">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G21" s="3">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H21" s="3">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I21" s="7">
-        <v>29</v>
+        <v>39.666666666666657</v>
       </c>
       <c r="J21" s="7">
-        <v>24</v>
+        <v>20.666666666666661</v>
       </c>
       <c r="K21" s="4">
-        <v>60.116619999999998</v>
+        <v>168.22362000000001</v>
       </c>
       <c r="L21" s="4">
-        <v>64.249750000000006</v>
+        <v>252.9239</v>
       </c>
       <c r="M21" s="4">
-        <v>56.032920000000011</v>
+        <v>168.41295333333329</v>
       </c>
       <c r="N21" s="4">
-        <v>2.9897540000000049</v>
+        <v>-50.82835600000007</v>
       </c>
       <c r="O21" s="5">
         <v>0</v>
       </c>
       <c r="P21" s="5">
-        <v>0.32124875000000003</v>
+        <v>2.529239</v>
       </c>
       <c r="Q21" s="6">
         <v>250</v>
@@ -1949,46 +1951,46 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>2002070</v>
+        <v>2022639</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C22" s="9">
-        <v>200207001140</v>
+        <v>200923800009</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F22" s="3">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H22" s="3">
+        <v>16</v>
+      </c>
+      <c r="I22" s="7">
         <v>24</v>
       </c>
-      <c r="I22" s="7">
-        <v>35.666666666666657</v>
-      </c>
       <c r="J22" s="7">
-        <v>31.666666666666661</v>
+        <v>28</v>
       </c>
       <c r="K22" s="4">
-        <v>129.97785999999999</v>
+        <v>202.36928</v>
       </c>
       <c r="L22" s="4">
-        <v>89.248149999999995</v>
+        <v>162.18248</v>
       </c>
       <c r="M22" s="4">
-        <v>87.747356666666676</v>
+        <v>0</v>
       </c>
       <c r="N22" s="4">
-        <v>16.04867800000001</v>
+        <v>-162.18248</v>
       </c>
       <c r="O22" s="5">
         <v>0</v>
@@ -2003,100 +2005,100 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>2022639</v>
+        <v>2002095</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="C23" s="9">
-        <v>200207300206</v>
+        <v>200209500324</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F23" s="3">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H23" s="3">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I23" s="7">
-        <v>37.666666666666657</v>
+        <v>21</v>
       </c>
       <c r="J23" s="7">
-        <v>35.666666666666657</v>
+        <v>28</v>
       </c>
       <c r="K23" s="4">
-        <v>71.592340000000007</v>
+        <v>37.425330000000002</v>
       </c>
       <c r="L23" s="4">
-        <v>74.919510000000002</v>
+        <v>60.609520000000003</v>
       </c>
       <c r="M23" s="4">
-        <v>0</v>
+        <v>25.730219999999999</v>
       </c>
       <c r="N23" s="4">
-        <v>-74.919510000000002</v>
+        <v>-29.733256000000001</v>
       </c>
       <c r="O23" s="5">
         <v>0</v>
       </c>
       <c r="P23" s="5">
-        <v>0</v>
+        <v>0.60609520000000006</v>
       </c>
       <c r="Q23" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R23" s="8"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>2022639</v>
+        <v>2005118</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C24" s="9">
-        <v>200207300363</v>
+        <v>200511801044</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F24" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G24" s="3">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H24" s="3">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I24" s="7">
-        <v>26.666666666666671</v>
+        <v>33.333333333333343</v>
       </c>
       <c r="J24" s="7">
-        <v>38.666666666666671</v>
+        <v>22.333333333333339</v>
       </c>
       <c r="K24" s="4">
-        <v>82.051349999999999</v>
+        <v>20.657029999999999</v>
       </c>
       <c r="L24" s="4">
-        <v>33.738280000000003</v>
+        <v>155.22092000000001</v>
       </c>
       <c r="M24" s="4">
-        <v>0</v>
+        <v>207.56238666666661</v>
       </c>
       <c r="N24" s="4">
-        <v>-33.738280000000003</v>
+        <v>93.853943999999927</v>
       </c>
       <c r="O24" s="5">
         <v>0</v>
@@ -2165,52 +2167,52 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>2009842</v>
+        <v>2022939</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C26" s="9">
-        <v>200209500038</v>
+        <v>201327000363</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G26" s="3">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="H26" s="3">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I26" s="7">
-        <v>35.666666666666657</v>
+        <v>52.333333333333343</v>
       </c>
       <c r="J26" s="7">
-        <v>30.666666666666661</v>
+        <v>34.333333333333343</v>
       </c>
       <c r="K26" s="4">
-        <v>20.814910000000001</v>
+        <v>117.83892</v>
       </c>
       <c r="L26" s="4">
-        <v>53.371960000000001</v>
+        <v>190.34692999999999</v>
       </c>
       <c r="M26" s="4">
-        <v>15.642896666666671</v>
+        <v>146.46358000000001</v>
       </c>
       <c r="N26" s="4">
-        <v>-34.600483999999987</v>
+        <v>-14.590634000000019</v>
       </c>
       <c r="O26" s="5">
         <v>0</v>
       </c>
       <c r="P26" s="5">
-        <v>0.53371960000000007</v>
+        <v>1.9034693</v>
       </c>
       <c r="Q26" s="6">
         <v>250</v>
@@ -2219,160 +2221,160 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>2002095</v>
+        <v>2022939</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C27" s="9">
-        <v>200209500324</v>
+        <v>200206700482</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="G27" s="3">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H27" s="3">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I27" s="7">
-        <v>21</v>
+        <v>50.666666666666657</v>
       </c>
       <c r="J27" s="7">
-        <v>28</v>
+        <v>44.666666666666657</v>
       </c>
       <c r="K27" s="4">
-        <v>37.425330000000002</v>
+        <v>132.01094000000001</v>
       </c>
       <c r="L27" s="4">
-        <v>60.609520000000003</v>
+        <v>117.13229</v>
       </c>
       <c r="M27" s="4">
-        <v>25.730219999999999</v>
+        <v>124.99812666666671</v>
       </c>
       <c r="N27" s="4">
-        <v>-29.733256000000001</v>
+        <v>32.865462000000051</v>
       </c>
       <c r="O27" s="5">
         <v>0</v>
       </c>
       <c r="P27" s="5">
-        <v>0.60609520000000006</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R27" s="8"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>2002095</v>
+        <v>2023085</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="C28" s="9">
-        <v>200209501067</v>
+        <v>201063400275</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="F28" s="3">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G28" s="3">
+        <v>30</v>
+      </c>
+      <c r="H28" s="3">
+        <v>27</v>
+      </c>
+      <c r="I28" s="7">
         <v>40</v>
       </c>
-      <c r="H28" s="3">
-        <v>5</v>
-      </c>
-      <c r="I28" s="7">
-        <v>11.66666666666667</v>
-      </c>
       <c r="J28" s="7">
-        <v>26.666666666666671</v>
+        <v>33</v>
       </c>
       <c r="K28" s="4">
-        <v>14.73837</v>
+        <v>79.80932</v>
       </c>
       <c r="L28" s="4">
-        <v>70.433459999999997</v>
+        <v>86.702029999999993</v>
       </c>
       <c r="M28" s="4">
-        <v>35.663876666666667</v>
+        <v>78.883646666666664</v>
       </c>
       <c r="N28" s="4">
-        <v>-27.636807999999991</v>
+        <v>7.9583460000000059</v>
       </c>
       <c r="O28" s="5">
         <v>0</v>
       </c>
       <c r="P28" s="5">
-        <v>0.70433460000000003</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R28" s="8"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>2002095</v>
+        <v>2023085</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="C29" s="9">
-        <v>200209501160</v>
+        <v>200405300324</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="F29" s="3">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G29" s="3">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H29" s="3">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I29" s="7">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J29" s="7">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K29" s="4">
-        <v>39.525309999999998</v>
+        <v>90.234579999999994</v>
       </c>
       <c r="L29" s="4">
-        <v>102.20468</v>
+        <v>99.252259999999993</v>
       </c>
       <c r="M29" s="4">
-        <v>53.586463333333327</v>
+        <v>67.55883333333334</v>
       </c>
       <c r="N29" s="4">
-        <v>-37.900924000000003</v>
+        <v>-18.18165999999999</v>
       </c>
       <c r="O29" s="5">
         <v>0</v>
       </c>
       <c r="P29" s="5">
-        <v>1.0220468</v>
+        <v>0.99252259999999992</v>
       </c>
       <c r="Q29" s="6">
         <v>250</v>
@@ -2381,52 +2383,52 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>2002095</v>
+        <v>2002060</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C30" s="9">
-        <v>200209501162</v>
+        <v>200206000020</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="3">
         <v>19</v>
       </c>
-      <c r="F30" s="3">
-        <v>16</v>
-      </c>
       <c r="G30" s="3">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="H30" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I30" s="7">
-        <v>22.666666666666671</v>
+        <v>36.333333333333343</v>
       </c>
       <c r="J30" s="7">
-        <v>31.666666666666671</v>
+        <v>34.333333333333343</v>
       </c>
       <c r="K30" s="4">
-        <v>17.68657</v>
+        <v>302.35682000000003</v>
       </c>
       <c r="L30" s="4">
-        <v>103.1444</v>
+        <v>568.03162999999995</v>
       </c>
       <c r="M30" s="4">
-        <v>66.654969999999992</v>
+        <v>476.47446999999988</v>
       </c>
       <c r="N30" s="4">
-        <v>-23.158436000000009</v>
+        <v>3.7377339999999322</v>
       </c>
       <c r="O30" s="5">
         <v>0</v>
       </c>
       <c r="P30" s="5">
-        <v>1.031444</v>
+        <v>4.2602372249999991</v>
       </c>
       <c r="Q30" s="6">
         <v>250</v>
@@ -2434,140 +2436,164 @@
       <c r="R30" s="8"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="A31" s="2">
+        <v>2023002</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="C31" s="9">
-        <v>200210502407</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+        <v>201074800404</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="F31" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G31" s="3">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H31" s="3">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I31" s="7">
-        <v>4.666666666666667</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="J31" s="7">
-        <v>3.6666666666666679</v>
+        <v>0.6666666666666643</v>
       </c>
       <c r="K31" s="4">
-        <v>28.37181</v>
+        <v>7.8948400000000003</v>
       </c>
       <c r="L31" s="4">
-        <v>53.864150000000002</v>
+        <v>53.256509999999999</v>
       </c>
       <c r="M31" s="4">
-        <v>0</v>
+        <v>17.212503333333331</v>
       </c>
       <c r="N31" s="4">
-        <v>-53.864150000000002</v>
+        <v>-32.601506000000001</v>
       </c>
       <c r="O31" s="5">
         <v>1500</v>
       </c>
       <c r="P31" s="5">
-        <v>0</v>
+        <v>0.53256510000000001</v>
       </c>
       <c r="Q31" s="6">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="R31" s="8"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+      <c r="A32" s="2">
+        <v>2002057</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C32" s="9">
-        <v>200210502426</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+        <v>200205700618</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H32" s="3">
-        <v>15</v>
-      </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="I32" s="7">
+        <v>6</v>
+      </c>
+      <c r="J32" s="7">
+        <v>6</v>
+      </c>
       <c r="K32" s="4">
         <v>0</v>
       </c>
       <c r="L32" s="4">
-        <v>65.215410000000006</v>
-      </c>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
+        <v>45.891080000000002</v>
+      </c>
+      <c r="M32" s="4">
+        <v>4.365593333333333</v>
+      </c>
+      <c r="N32" s="4">
+        <v>-40.652368000000003</v>
+      </c>
       <c r="O32" s="5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P32" s="5">
-        <v>0</v>
+        <v>0.45891080000000001</v>
       </c>
       <c r="Q32" s="6">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="R32" s="8"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>2023085</v>
+        <v>2023177</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C33" s="9">
-        <v>200405300324</v>
+        <v>202317700120</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="F33" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G33" s="3">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H33" s="3">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I33" s="7">
-        <v>33</v>
+        <v>28.333333333333329</v>
       </c>
       <c r="J33" s="7">
-        <v>27</v>
+        <v>32.333333333333329</v>
       </c>
       <c r="K33" s="4">
-        <v>90.234579999999994</v>
+        <v>74.071690000000004</v>
       </c>
       <c r="L33" s="4">
-        <v>99.252259999999993</v>
+        <v>62.208060000000003</v>
       </c>
       <c r="M33" s="4">
-        <v>67.55883333333334</v>
+        <v>66.375219999999999</v>
       </c>
       <c r="N33" s="4">
-        <v>-18.18165999999999</v>
+        <v>17.44220399999999</v>
       </c>
       <c r="O33" s="5">
         <v>0</v>
       </c>
       <c r="P33" s="5">
-        <v>0.99252259999999992</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R33" s="8"/>
     </row>
@@ -2579,100 +2605,100 @@
         <v>59</v>
       </c>
       <c r="C34" s="9">
-        <v>200405300624</v>
+        <v>201636400069</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F34" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G34" s="3">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H34" s="3">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="I34" s="7">
-        <v>39.666666666666657</v>
+        <v>43.333333333333343</v>
       </c>
       <c r="J34" s="7">
-        <v>20.666666666666661</v>
+        <v>41.333333333333343</v>
       </c>
       <c r="K34" s="4">
-        <v>168.22362000000001</v>
+        <v>87.600129999999993</v>
       </c>
       <c r="L34" s="4">
-        <v>252.9239</v>
+        <v>71.982050000000001</v>
       </c>
       <c r="M34" s="4">
-        <v>168.41295333333329</v>
+        <v>81.972930000000005</v>
       </c>
       <c r="N34" s="4">
-        <v>-50.82835600000007</v>
+        <v>26.385466000000012</v>
       </c>
       <c r="O34" s="5">
         <v>0</v>
       </c>
       <c r="P34" s="5">
-        <v>2.529239</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R34" s="8"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>2022939</v>
+        <v>2002095</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="C35" s="9">
-        <v>200511800890</v>
+        <v>200209501160</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F35" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G35" s="3">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H35" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>12.66666666666667</v>
+        <v>23</v>
       </c>
       <c r="J35" s="7">
-        <v>10.66666666666667</v>
+        <v>34</v>
       </c>
       <c r="K35" s="4">
-        <v>57.349049999999998</v>
+        <v>39.525309999999998</v>
       </c>
       <c r="L35" s="4">
-        <v>97.37</v>
+        <v>102.20468</v>
       </c>
       <c r="M35" s="4">
-        <v>49.703740000000003</v>
+        <v>53.586463333333327</v>
       </c>
       <c r="N35" s="4">
-        <v>-37.725512000000002</v>
+        <v>-37.900924000000003</v>
       </c>
       <c r="O35" s="5">
         <v>0</v>
       </c>
       <c r="P35" s="5">
-        <v>0.97370000000000012</v>
+        <v>1.0220468</v>
       </c>
       <c r="Q35" s="6">
         <v>250</v>
@@ -2687,40 +2713,40 @@
         <v>64</v>
       </c>
       <c r="C36" s="9">
-        <v>200511801044</v>
+        <v>200660400395</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F36" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G36" s="3">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H36" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I36" s="7">
-        <v>33.333333333333343</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="J36" s="7">
-        <v>22.333333333333339</v>
+        <v>31.333333333333329</v>
       </c>
       <c r="K36" s="4">
-        <v>20.657029999999999</v>
+        <v>16.055330000000001</v>
       </c>
       <c r="L36" s="4">
-        <v>155.22092000000001</v>
+        <v>13.556190000000001</v>
       </c>
       <c r="M36" s="4">
-        <v>207.56238666666661</v>
+        <v>36.101503333333334</v>
       </c>
       <c r="N36" s="4">
-        <v>93.853943999999927</v>
+        <v>29.765613999999999</v>
       </c>
       <c r="O36" s="5">
         <v>0</v>
@@ -2735,306 +2761,322 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>2023002</v>
+        <v>2002057</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C37" s="9">
-        <v>200625400127</v>
+        <v>200205700151</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F37" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G37" s="3">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H37" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>10.33333333333333</v>
+        <v>19.666666666666671</v>
       </c>
       <c r="J37" s="7">
-        <v>-15.66666666666667</v>
+        <v>33.666666666666671</v>
       </c>
       <c r="K37" s="4">
-        <v>26.232510000000001</v>
+        <v>30.21284</v>
       </c>
       <c r="L37" s="4">
-        <v>135.21021999999999</v>
+        <v>21.680890000000002</v>
       </c>
       <c r="M37" s="4">
-        <v>21.504180000000002</v>
+        <v>27.61830333333333</v>
       </c>
       <c r="N37" s="4">
-        <v>-109.405204</v>
+        <v>11.461073999999989</v>
       </c>
       <c r="O37" s="5">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P37" s="5">
-        <v>1.3521022</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="6">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="R37" s="8"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>2021125</v>
+        <v>2022639</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C38" s="9">
-        <v>200625400735</v>
+        <v>200207300206</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F38" s="3">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G38" s="3">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H38" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I38" s="7">
-        <v>13.33333333333333</v>
+        <v>37.666666666666657</v>
       </c>
       <c r="J38" s="7">
-        <v>10.33333333333333</v>
+        <v>35.666666666666657</v>
       </c>
       <c r="K38" s="4">
-        <v>29.761990000000001</v>
+        <v>71.592340000000007</v>
       </c>
       <c r="L38" s="4">
-        <v>59.051720000000003</v>
+        <v>74.919510000000002</v>
       </c>
       <c r="M38" s="4">
-        <v>9.2596433333333348</v>
+        <v>0</v>
       </c>
       <c r="N38" s="4">
-        <v>-47.940148000000001</v>
+        <v>-74.919510000000002</v>
       </c>
       <c r="O38" s="5">
         <v>0</v>
       </c>
       <c r="P38" s="5">
-        <v>0.59051720000000008</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R38" s="8"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>2005118</v>
+        <v>2022939</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C39" s="9">
-        <v>200660400395</v>
+        <v>200206700519</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F39" s="3">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G39" s="3">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="H39" s="3">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="I39" s="7">
-        <v>13.33333333333333</v>
+        <v>40.666666666666657</v>
       </c>
       <c r="J39" s="7">
-        <v>31.333333333333329</v>
+        <v>17.666666666666661</v>
       </c>
       <c r="K39" s="4">
-        <v>16.055330000000001</v>
+        <v>56.670520000000003</v>
       </c>
       <c r="L39" s="4">
-        <v>13.556190000000001</v>
+        <v>110.0772</v>
       </c>
       <c r="M39" s="4">
-        <v>36.101503333333334</v>
+        <v>62.187460000000009</v>
       </c>
       <c r="N39" s="4">
-        <v>29.765613999999999</v>
+        <v>-35.452247999999997</v>
       </c>
       <c r="O39" s="5">
         <v>0</v>
       </c>
       <c r="P39" s="5">
-        <v>0</v>
+        <v>1.1007720000000001</v>
       </c>
       <c r="Q39" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R39" s="8"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
+      <c r="A40" s="2">
+        <v>2022939</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C40" s="9">
-        <v>200848700017</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+        <v>202293900019</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F40" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G40" s="3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H40" s="3">
-        <v>9</v>
-      </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="I40" s="7">
+        <v>44</v>
+      </c>
+      <c r="J40" s="7">
+        <v>44</v>
+      </c>
       <c r="K40" s="4">
-        <v>0</v>
+        <v>109.84516000000001</v>
       </c>
       <c r="L40" s="4">
-        <v>24.178380000000001</v>
-      </c>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
+        <v>66.066460000000006</v>
+      </c>
+      <c r="M40" s="4">
+        <v>53.717599999999997</v>
+      </c>
+      <c r="N40" s="4">
+        <v>-1.605340000000012</v>
+      </c>
       <c r="O40" s="5">
         <v>0</v>
       </c>
       <c r="P40" s="5">
-        <v>0</v>
+        <v>0.66066460000000005</v>
       </c>
       <c r="Q40" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R40" s="8"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>2022639</v>
+        <v>2022939</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C41" s="9">
-        <v>200923800009</v>
+        <v>200511800890</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F41" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G41" s="3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H41" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I41" s="7">
-        <v>24</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="J41" s="7">
-        <v>28</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="K41" s="4">
-        <v>202.36928</v>
+        <v>57.349049999999998</v>
       </c>
       <c r="L41" s="4">
-        <v>162.18248</v>
+        <v>97.37</v>
       </c>
       <c r="M41" s="4">
-        <v>0</v>
+        <v>49.703740000000003</v>
       </c>
       <c r="N41" s="4">
-        <v>-162.18248</v>
+        <v>-37.725512000000002</v>
       </c>
       <c r="O41" s="5">
         <v>0</v>
       </c>
       <c r="P41" s="5">
-        <v>0</v>
+        <v>0.97370000000000012</v>
       </c>
       <c r="Q41" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R41" s="8"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>2009842</v>
+        <v>2002095</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C42" s="9">
-        <v>200984200153</v>
+        <v>200205300429</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F42" s="3">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G42" s="3">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="H42" s="3">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I42" s="7">
-        <v>38.666666666666657</v>
+        <v>24</v>
       </c>
       <c r="J42" s="7">
-        <v>16.666666666666661</v>
+        <v>26</v>
       </c>
       <c r="K42" s="4">
-        <v>18.039950000000001</v>
+        <v>41.613610000000001</v>
       </c>
       <c r="L42" s="4">
-        <v>87.546790000000001</v>
+        <v>64.495710000000003</v>
       </c>
       <c r="M42" s="4">
-        <v>10.75553666666667</v>
+        <v>45.956506666666677</v>
       </c>
       <c r="N42" s="4">
-        <v>-74.640146000000001</v>
+        <v>-9.3479019999999906</v>
       </c>
       <c r="O42" s="5">
         <v>0</v>
       </c>
       <c r="P42" s="5">
-        <v>0.87546790000000008</v>
+        <v>0.64495710000000006</v>
       </c>
       <c r="Q42" s="6">
         <v>250</v>
@@ -3043,106 +3085,106 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>2009842</v>
+        <v>2023177</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="C43" s="9">
-        <v>200984200845</v>
+        <v>202317700141</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F43" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G43" s="3">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="H43" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I43" s="7">
-        <v>20</v>
+        <v>24.333333333333329</v>
       </c>
       <c r="J43" s="7">
-        <v>19</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="K43" s="4">
-        <v>8.8895699999999991</v>
+        <v>20.782160000000001</v>
       </c>
       <c r="L43" s="4">
-        <v>63.370780000000003</v>
+        <v>29.47757</v>
       </c>
       <c r="M43" s="4">
-        <v>18.51793</v>
+        <v>41.320500000000003</v>
       </c>
       <c r="N43" s="4">
-        <v>-41.149264000000002</v>
+        <v>20.107030000000002</v>
       </c>
       <c r="O43" s="5">
         <v>0</v>
       </c>
       <c r="P43" s="5">
-        <v>0.63370779999999993</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R43" s="8"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>2009842</v>
+        <v>2022939</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C44" s="9">
-        <v>200984201066</v>
+        <v>202293900020</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F44" s="3">
+        <v>24</v>
+      </c>
+      <c r="G44" s="3">
+        <v>24</v>
+      </c>
+      <c r="H44" s="3">
         <v>14</v>
       </c>
-      <c r="G44" s="3">
-        <v>16</v>
-      </c>
-      <c r="H44" s="3">
-        <v>15</v>
-      </c>
       <c r="I44" s="7">
-        <v>21</v>
+        <v>24.333333333333329</v>
       </c>
       <c r="J44" s="7">
-        <v>26</v>
+        <v>30.333333333333329</v>
       </c>
       <c r="K44" s="4">
-        <v>8.0576299999999996</v>
+        <v>46.2059</v>
       </c>
       <c r="L44" s="4">
-        <v>35.567520000000002</v>
+        <v>31.27309</v>
       </c>
       <c r="M44" s="4">
-        <v>11.26651333333333</v>
+        <v>28.102313333333331</v>
       </c>
       <c r="N44" s="4">
-        <v>-22.047704</v>
+        <v>2.4496859999999958</v>
       </c>
       <c r="O44" s="5">
         <v>0</v>
       </c>
       <c r="P44" s="5">
-        <v>0.35567520000000002</v>
+        <v>0.15636544999999999</v>
       </c>
       <c r="Q44" s="6">
         <v>250</v>
@@ -3151,52 +3193,52 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>2023085</v>
+        <v>2022939</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C45" s="9">
-        <v>201063400142</v>
+        <v>201899300053</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="F45" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G45" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H45" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I45" s="7">
-        <v>30</v>
+        <v>24.333333333333329</v>
       </c>
       <c r="J45" s="7">
-        <v>25</v>
+        <v>25.333333333333329</v>
       </c>
       <c r="K45" s="4">
-        <v>114.90956</v>
+        <v>43.482939999999999</v>
       </c>
       <c r="L45" s="4">
-        <v>93.199730000000002</v>
+        <v>55.590969999999999</v>
       </c>
       <c r="M45" s="4">
-        <v>78.631203333333346</v>
+        <v>37.893526666666673</v>
       </c>
       <c r="N45" s="4">
-        <v>1.157714000000013</v>
+        <v>-10.11873799999999</v>
       </c>
       <c r="O45" s="5">
         <v>0</v>
       </c>
       <c r="P45" s="5">
-        <v>0.69899797499999994</v>
+        <v>0.55590969999999995</v>
       </c>
       <c r="Q45" s="6">
         <v>250</v>
@@ -3205,55 +3247,55 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>2023085</v>
+        <v>2002060</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C46" s="9">
-        <v>201063400275</v>
+        <v>200206000084</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="F46" s="3">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G46" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H46" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I46" s="7">
-        <v>40</v>
+        <v>35.666666666666657</v>
       </c>
       <c r="J46" s="7">
-        <v>33</v>
+        <v>30.666666666666661</v>
       </c>
       <c r="K46" s="4">
-        <v>79.80932</v>
+        <v>109.97247</v>
       </c>
       <c r="L46" s="4">
-        <v>86.702029999999993</v>
+        <v>194.62161</v>
       </c>
       <c r="M46" s="4">
-        <v>78.883646666666664</v>
+        <v>137.57176666666669</v>
       </c>
       <c r="N46" s="4">
-        <v>7.9583460000000059</v>
+        <v>-29.535489999999982</v>
       </c>
       <c r="O46" s="5">
         <v>0</v>
       </c>
       <c r="P46" s="5">
-        <v>0</v>
+        <v>1.9462161</v>
       </c>
       <c r="Q46" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R46" s="8"/>
     </row>
@@ -3265,46 +3307,46 @@
         <v>67</v>
       </c>
       <c r="C47" s="9">
-        <v>201074800326</v>
+        <v>200625400127</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F47" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G47" s="3">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H47" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I47" s="7">
-        <v>7.333333333333333</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="J47" s="7">
-        <v>-22.666666666666671</v>
+        <v>-15.66666666666667</v>
       </c>
       <c r="K47" s="4">
-        <v>23.7637</v>
+        <v>26.232510000000001</v>
       </c>
       <c r="L47" s="4">
-        <v>108.67234999999999</v>
+        <v>135.21021999999999</v>
       </c>
       <c r="M47" s="4">
-        <v>16.91567666666667</v>
+        <v>21.504180000000002</v>
       </c>
       <c r="N47" s="4">
-        <v>-88.373537999999996</v>
+        <v>-109.405204</v>
       </c>
       <c r="O47" s="5">
         <v>2000</v>
       </c>
       <c r="P47" s="5">
-        <v>1.0867235</v>
+        <v>1.3521022</v>
       </c>
       <c r="Q47" s="6">
         <v>500</v>
@@ -3313,106 +3355,106 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>2023002</v>
+        <v>2002060</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="C48" s="9">
-        <v>201074800404</v>
+        <v>200206000006</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F48" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G48" s="3">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H48" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I48" s="7">
-        <v>8.6666666666666661</v>
+        <v>16.333333333333329</v>
       </c>
       <c r="J48" s="7">
-        <v>0.6666666666666643</v>
+        <v>16.333333333333329</v>
       </c>
       <c r="K48" s="4">
-        <v>7.8948400000000003</v>
+        <v>41.232799999999997</v>
       </c>
       <c r="L48" s="4">
-        <v>53.256509999999999</v>
+        <v>65.255870000000002</v>
       </c>
       <c r="M48" s="4">
-        <v>17.212503333333331</v>
+        <v>45.289326666666661</v>
       </c>
       <c r="N48" s="4">
-        <v>-32.601506000000001</v>
+        <v>-10.908678000000011</v>
       </c>
       <c r="O48" s="5">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="P48" s="5">
-        <v>0.53256510000000001</v>
+        <v>0.65255870000000005</v>
       </c>
       <c r="Q48" s="6">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="R48" s="8"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>2011731</v>
+        <v>2022939</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C49" s="9">
-        <v>201173100172</v>
+        <v>201327000069</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F49" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G49" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H49" s="3">
         <v>16</v>
       </c>
       <c r="I49" s="7">
-        <v>19</v>
+        <v>18.666666666666671</v>
       </c>
       <c r="J49" s="7">
-        <v>23</v>
+        <v>22.666666666666671</v>
       </c>
       <c r="K49" s="4">
-        <v>29.148759999999999</v>
+        <v>79.283459999999991</v>
       </c>
       <c r="L49" s="4">
-        <v>39.288800000000002</v>
+        <v>174.4933</v>
       </c>
       <c r="M49" s="4">
-        <v>19.30109666666667</v>
+        <v>101.9252133333333</v>
       </c>
       <c r="N49" s="4">
-        <v>-16.127483999999999</v>
+        <v>-52.183044000000052</v>
       </c>
       <c r="O49" s="5">
         <v>0</v>
       </c>
       <c r="P49" s="5">
-        <v>0.39288800000000001</v>
+        <v>1.7449330000000001</v>
       </c>
       <c r="Q49" s="6">
         <v>250</v>
@@ -3421,106 +3463,106 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>2011731</v>
+        <v>2021125</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="C50" s="9">
-        <v>201173100249</v>
+        <v>202112500012</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="F50" s="3">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G50" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H50" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I50" s="7">
-        <v>46</v>
+        <v>17.333333333333329</v>
       </c>
       <c r="J50" s="7">
-        <v>41</v>
+        <v>16.333333333333329</v>
       </c>
       <c r="K50" s="4">
-        <v>123.67565</v>
+        <v>9.4154800000000005</v>
       </c>
       <c r="L50" s="4">
-        <v>121.34884</v>
+        <v>30.034099999999999</v>
       </c>
       <c r="M50" s="4">
-        <v>116.26441333333329</v>
+        <v>4.1351266666666664</v>
       </c>
       <c r="N50" s="4">
-        <v>18.16845599999996</v>
+        <v>-25.071947999999999</v>
       </c>
       <c r="O50" s="5">
         <v>0</v>
       </c>
       <c r="P50" s="5">
-        <v>0</v>
+        <v>0.30034100000000002</v>
       </c>
       <c r="Q50" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R50" s="8"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>2018993</v>
+        <v>2002057</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C51" s="9">
-        <v>201178500076</v>
+        <v>200205700384</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F51" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="G51" s="3">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="H51" s="3">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>62</v>
+        <v>19.666666666666671</v>
       </c>
       <c r="J51" s="7">
-        <v>33</v>
+        <v>31.666666666666671</v>
       </c>
       <c r="K51" s="4">
-        <v>233.78666000000001</v>
+        <v>24.68084</v>
       </c>
       <c r="L51" s="4">
-        <v>251.11296999999999</v>
+        <v>28.490580000000001</v>
       </c>
       <c r="M51" s="4">
-        <v>211.11028333333331</v>
+        <v>25.18221333333333</v>
       </c>
       <c r="N51" s="4">
-        <v>2.219369999999941</v>
+        <v>1.728075999999994</v>
       </c>
       <c r="O51" s="5">
         <v>0</v>
       </c>
       <c r="P51" s="5">
-        <v>1.883347275</v>
+        <v>0.14245289999999999</v>
       </c>
       <c r="Q51" s="6">
         <v>250</v>
@@ -3529,160 +3571,160 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>2018993</v>
+        <v>2022639</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C52" s="9">
-        <v>201178500087</v>
+        <v>202263900079</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F52" s="3">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G52" s="3">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H52" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I52" s="7">
-        <v>29</v>
+        <v>41.666666666666657</v>
       </c>
       <c r="J52" s="7">
-        <v>27</v>
+        <v>34.666666666666657</v>
       </c>
       <c r="K52" s="4">
-        <v>62.757689999999997</v>
+        <v>117.75586</v>
       </c>
       <c r="L52" s="4">
-        <v>67.887879999999996</v>
+        <v>114.47995</v>
       </c>
       <c r="M52" s="4">
-        <v>58.533586666666672</v>
+        <v>0</v>
       </c>
       <c r="N52" s="4">
-        <v>2.3524240000000129</v>
+        <v>-114.47995</v>
       </c>
       <c r="O52" s="5">
         <v>0</v>
       </c>
       <c r="P52" s="5">
-        <v>0.50915909999999998</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R52" s="8"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
-        <v>2022679</v>
+        <v>2002095</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="C53" s="9">
-        <v>201294400165</v>
+        <v>200209501067</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F53" s="3">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="G53" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H53" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>46</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="J53" s="7">
-        <v>42</v>
+        <v>26.666666666666671</v>
       </c>
       <c r="K53" s="4">
-        <v>99.850290000000001</v>
+        <v>14.73837</v>
       </c>
       <c r="L53" s="4">
-        <v>81.764769999999999</v>
+        <v>70.433459999999997</v>
       </c>
       <c r="M53" s="4">
-        <v>83.753239999999991</v>
+        <v>35.663876666666667</v>
       </c>
       <c r="N53" s="4">
-        <v>18.739117999999991</v>
+        <v>-27.636807999999991</v>
       </c>
       <c r="O53" s="5">
         <v>0</v>
       </c>
       <c r="P53" s="5">
-        <v>0</v>
+        <v>0.70433460000000003</v>
       </c>
       <c r="Q53" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R53" s="8"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>2022679</v>
+        <v>2021125</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C54" s="9">
-        <v>201294400279</v>
+        <v>200625400735</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F54" s="3">
+        <v>15</v>
+      </c>
+      <c r="G54" s="3">
         <v>43</v>
       </c>
-      <c r="G54" s="3">
-        <v>61</v>
-      </c>
       <c r="H54" s="3">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="I54" s="7">
-        <v>45.333333333333343</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="J54" s="7">
-        <v>23.333333333333339</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K54" s="4">
-        <v>72.272829999999999</v>
+        <v>29.761990000000001</v>
       </c>
       <c r="L54" s="4">
-        <v>111.96988</v>
+        <v>59.051720000000003</v>
       </c>
       <c r="M54" s="4">
-        <v>83.111879999999999</v>
+        <v>9.2596433333333348</v>
       </c>
       <c r="N54" s="4">
-        <v>-12.235624</v>
+        <v>-47.940148000000001</v>
       </c>
       <c r="O54" s="5">
         <v>0</v>
       </c>
       <c r="P54" s="5">
-        <v>1.1196988000000001</v>
+        <v>0.59051720000000008</v>
       </c>
       <c r="Q54" s="6">
         <v>250</v>
@@ -3691,160 +3733,160 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>2022679</v>
+        <v>2011731</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="C55" s="9">
-        <v>201294400281</v>
+        <v>201173100249</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="F55" s="3">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G55" s="3">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H55" s="3">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="I55" s="7">
-        <v>45.333333333333343</v>
+        <v>46</v>
       </c>
       <c r="J55" s="7">
-        <v>20.333333333333339</v>
+        <v>41</v>
       </c>
       <c r="K55" s="4">
-        <v>157.05233999999999</v>
+        <v>123.67565</v>
       </c>
       <c r="L55" s="4">
-        <v>215.43922000000001</v>
+        <v>121.34884</v>
       </c>
       <c r="M55" s="4">
-        <v>153.32597000000001</v>
+        <v>116.26441333333329</v>
       </c>
       <c r="N55" s="4">
-        <v>-31.448056000000008</v>
+        <v>18.16845599999996</v>
       </c>
       <c r="O55" s="5">
         <v>0</v>
       </c>
       <c r="P55" s="5">
-        <v>2.1543922000000002</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R55" s="8"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>2022679</v>
+        <v>2022639</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C56" s="9">
-        <v>201294400288</v>
+        <v>201330600206</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F56" s="3">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G56" s="3">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H56" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I56" s="7">
-        <v>50.333333333333343</v>
+        <v>28.333333333333329</v>
       </c>
       <c r="J56" s="7">
-        <v>45.333333333333343</v>
+        <v>25.333333333333329</v>
       </c>
       <c r="K56" s="4">
-        <v>92.417149999999992</v>
+        <v>30.345659999999999</v>
       </c>
       <c r="L56" s="4">
-        <v>66.352029999999999</v>
+        <v>64.565780000000004</v>
       </c>
       <c r="M56" s="4">
-        <v>59.695973333333328</v>
+        <v>0</v>
       </c>
       <c r="N56" s="4">
-        <v>5.2831379999999939</v>
+        <v>-64.565780000000004</v>
       </c>
       <c r="O56" s="5">
         <v>0</v>
       </c>
       <c r="P56" s="5">
-        <v>0.33176014999999998</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R56" s="8"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
-        <v>2022939</v>
+        <v>2009842</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C57" s="9">
-        <v>201327000069</v>
+        <v>200984200153</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F57" s="3">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G57" s="3">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="H57" s="3">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I57" s="7">
-        <v>18.666666666666671</v>
+        <v>38.666666666666657</v>
       </c>
       <c r="J57" s="7">
-        <v>22.666666666666671</v>
+        <v>16.666666666666661</v>
       </c>
       <c r="K57" s="4">
-        <v>79.283459999999991</v>
+        <v>18.039950000000001</v>
       </c>
       <c r="L57" s="4">
-        <v>174.4933</v>
+        <v>87.546790000000001</v>
       </c>
       <c r="M57" s="4">
-        <v>101.9252133333333</v>
+        <v>10.75553666666667</v>
       </c>
       <c r="N57" s="4">
-        <v>-52.183044000000052</v>
+        <v>-74.640146000000001</v>
       </c>
       <c r="O57" s="5">
         <v>0</v>
       </c>
       <c r="P57" s="5">
-        <v>1.7449330000000001</v>
+        <v>0.87546790000000008</v>
       </c>
       <c r="Q57" s="6">
         <v>250</v>
@@ -3853,160 +3895,160 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
-        <v>2022939</v>
+        <v>2002070</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C58" s="9">
-        <v>201327000073</v>
+        <v>200207001140</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F58" s="3">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G58" s="3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H58" s="3">
         <v>24</v>
       </c>
       <c r="I58" s="7">
-        <v>31.333333333333329</v>
+        <v>35.666666666666657</v>
       </c>
       <c r="J58" s="7">
-        <v>27.333333333333329</v>
+        <v>31.666666666666661</v>
       </c>
       <c r="K58" s="4">
-        <v>68.409880000000001</v>
+        <v>129.97785999999999</v>
       </c>
       <c r="L58" s="4">
-        <v>85.947040000000001</v>
+        <v>89.248149999999995</v>
       </c>
       <c r="M58" s="4">
-        <v>49.752850000000002</v>
+        <v>87.747356666666676</v>
       </c>
       <c r="N58" s="4">
-        <v>-26.24362</v>
+        <v>16.04867800000001</v>
       </c>
       <c r="O58" s="5">
         <v>0</v>
       </c>
       <c r="P58" s="5">
-        <v>0.85947040000000008</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R58" s="8"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
-        <v>2022939</v>
+        <v>2002070</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C59" s="9">
-        <v>201327000332</v>
+        <v>200207001063</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F59" s="3">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G59" s="3">
+        <v>32</v>
+      </c>
+      <c r="H59" s="3">
+        <v>25</v>
+      </c>
+      <c r="I59" s="7">
+        <v>29</v>
+      </c>
+      <c r="J59" s="7">
         <v>24</v>
       </c>
-      <c r="H59" s="3">
-        <v>13</v>
-      </c>
-      <c r="I59" s="7">
-        <v>43.333333333333343</v>
-      </c>
-      <c r="J59" s="7">
-        <v>50.333333333333343</v>
-      </c>
       <c r="K59" s="4">
-        <v>66.997240000000005</v>
+        <v>60.116619999999998</v>
       </c>
       <c r="L59" s="4">
-        <v>24.459119999999999</v>
+        <v>64.249750000000006</v>
       </c>
       <c r="M59" s="4">
-        <v>34.158923333333327</v>
+        <v>56.032920000000011</v>
       </c>
       <c r="N59" s="4">
-        <v>16.531587999999989</v>
+        <v>2.9897540000000049</v>
       </c>
       <c r="O59" s="5">
         <v>0</v>
       </c>
       <c r="P59" s="5">
-        <v>0</v>
+        <v>0.32124875000000003</v>
       </c>
       <c r="Q59" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R59" s="8"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
-        <v>2022939</v>
+        <v>2023085</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C60" s="9">
-        <v>201327000363</v>
+        <v>202308500082</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="F60" s="3">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G60" s="3">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="H60" s="3">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="I60" s="7">
-        <v>52.333333333333343</v>
+        <v>15.66666666666667</v>
       </c>
       <c r="J60" s="7">
-        <v>34.333333333333343</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="K60" s="4">
-        <v>117.83892</v>
+        <v>24.048690000000001</v>
       </c>
       <c r="L60" s="4">
-        <v>190.34692999999999</v>
+        <v>35.72383</v>
       </c>
       <c r="M60" s="4">
-        <v>146.46358000000001</v>
+        <v>22.844533333333331</v>
       </c>
       <c r="N60" s="4">
-        <v>-14.590634000000019</v>
+        <v>-8.3103900000000017</v>
       </c>
       <c r="O60" s="5">
         <v>0</v>
       </c>
       <c r="P60" s="5">
-        <v>1.9034693</v>
+        <v>0.35723830000000001</v>
       </c>
       <c r="Q60" s="6">
         <v>250</v>
@@ -4015,109 +4057,109 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
-        <v>2022639</v>
+        <v>2022939</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C61" s="9">
-        <v>201330600206</v>
+        <v>201899300414</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F61" s="3">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G61" s="3">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H61" s="3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I61" s="7">
-        <v>28.333333333333329</v>
+        <v>36.666666666666657</v>
       </c>
       <c r="J61" s="7">
-        <v>25.333333333333329</v>
+        <v>27.666666666666661</v>
       </c>
       <c r="K61" s="4">
-        <v>30.345659999999999</v>
+        <v>85.553660000000008</v>
       </c>
       <c r="L61" s="4">
-        <v>64.565780000000004</v>
+        <v>115.84715</v>
       </c>
       <c r="M61" s="4">
-        <v>0</v>
+        <v>86.13788333333332</v>
       </c>
       <c r="N61" s="4">
-        <v>-64.565780000000004</v>
+        <v>-12.481690000000009</v>
       </c>
       <c r="O61" s="5">
         <v>0</v>
       </c>
       <c r="P61" s="5">
-        <v>0</v>
+        <v>1.1584715000000001</v>
       </c>
       <c r="Q61" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R61" s="8"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
-        <v>2023303</v>
+        <v>2022939</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="C62" s="9">
-        <v>201330600340</v>
+        <v>201330600476</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F62" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G62" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H62" s="3">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I62" s="7">
-        <v>13.66666666666667</v>
+        <v>47.666666666666657</v>
       </c>
       <c r="J62" s="7">
-        <v>16.666666666666671</v>
+        <v>37.666666666666657</v>
       </c>
       <c r="K62" s="4">
-        <v>83.232339999999994</v>
+        <v>99.547849999999997</v>
       </c>
       <c r="L62" s="4">
-        <v>57.942810000000001</v>
+        <v>145.1636</v>
       </c>
       <c r="M62" s="4">
-        <v>0</v>
+        <v>109.4187566666667</v>
       </c>
       <c r="N62" s="4">
-        <v>-57.942810000000001</v>
+        <v>-13.86109199999999</v>
       </c>
       <c r="O62" s="5">
         <v>0</v>
       </c>
       <c r="P62" s="5">
-        <v>0</v>
+        <v>1.4516359999999999</v>
       </c>
       <c r="Q62" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R62" s="8"/>
     </row>
@@ -4129,46 +4171,46 @@
         <v>41</v>
       </c>
       <c r="C63" s="9">
-        <v>201330600476</v>
+        <v>201899300223</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F63" s="3">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G63" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H63" s="3">
+        <v>10</v>
+      </c>
+      <c r="I63" s="7">
+        <v>20</v>
+      </c>
+      <c r="J63" s="7">
         <v>30</v>
       </c>
-      <c r="I63" s="7">
-        <v>47.666666666666657</v>
-      </c>
-      <c r="J63" s="7">
-        <v>37.666666666666657</v>
-      </c>
       <c r="K63" s="4">
-        <v>99.547849999999997</v>
+        <v>27.107030000000002</v>
       </c>
       <c r="L63" s="4">
-        <v>145.1636</v>
+        <v>33.319200000000002</v>
       </c>
       <c r="M63" s="4">
-        <v>109.4187566666667</v>
+        <v>28.339396666666669</v>
       </c>
       <c r="N63" s="4">
-        <v>-13.86109199999999</v>
+        <v>0.68807600000000235</v>
       </c>
       <c r="O63" s="5">
         <v>0</v>
       </c>
       <c r="P63" s="5">
-        <v>1.4516359999999999</v>
+        <v>0.24989400000000001</v>
       </c>
       <c r="Q63" s="6">
         <v>250</v>
@@ -4177,52 +4219,52 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
-        <v>2018993</v>
+        <v>2009842</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C64" s="9">
-        <v>201613300250</v>
+        <v>200209500038</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F64" s="3">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G64" s="3">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="H64" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I64" s="7">
-        <v>30.333333333333329</v>
+        <v>35.666666666666657</v>
       </c>
       <c r="J64" s="7">
-        <v>24.333333333333329</v>
+        <v>30.666666666666661</v>
       </c>
       <c r="K64" s="4">
-        <v>36.459760000000003</v>
+        <v>20.814910000000001</v>
       </c>
       <c r="L64" s="4">
-        <v>58.332389999999997</v>
+        <v>53.371960000000001</v>
       </c>
       <c r="M64" s="4">
-        <v>31.68701333333334</v>
+        <v>15.642896666666671</v>
       </c>
       <c r="N64" s="4">
-        <v>-20.307973999999991</v>
+        <v>-34.600483999999987</v>
       </c>
       <c r="O64" s="5">
         <v>0</v>
       </c>
       <c r="P64" s="5">
-        <v>0.58332390000000001</v>
+        <v>0.53371960000000007</v>
       </c>
       <c r="Q64" s="6">
         <v>250</v>
@@ -4231,52 +4273,52 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
-        <v>2018993</v>
+        <v>2022679</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="C65" s="9">
-        <v>201613300337</v>
+        <v>201294400281</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F65" s="3">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G65" s="3">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="H65" s="3">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I65" s="7">
-        <v>35.333333333333343</v>
+        <v>45.333333333333343</v>
       </c>
       <c r="J65" s="7">
-        <v>25.333333333333339</v>
+        <v>20.333333333333339</v>
       </c>
       <c r="K65" s="4">
-        <v>106.73451</v>
+        <v>157.05233999999999</v>
       </c>
       <c r="L65" s="4">
-        <v>76.190640000000002</v>
+        <v>215.43922000000001</v>
       </c>
       <c r="M65" s="4">
-        <v>67.08329333333333</v>
+        <v>153.32597000000001</v>
       </c>
       <c r="N65" s="4">
-        <v>4.3093119999999914</v>
+        <v>-31.448056000000008</v>
       </c>
       <c r="O65" s="5">
         <v>0</v>
       </c>
       <c r="P65" s="5">
-        <v>0.38095319999999999</v>
+        <v>2.1543922000000002</v>
       </c>
       <c r="Q65" s="6">
         <v>250</v>
@@ -4284,39 +4326,47 @@
       <c r="R65" s="8"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="A66" s="2">
+        <v>2011731</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C66" s="9">
-        <v>201624800468</v>
-      </c>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
+        <v>200205700568</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="F66" s="3">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G66" s="3">
+        <v>42</v>
+      </c>
+      <c r="H66" s="3">
         <v>32</v>
       </c>
-      <c r="H66" s="3">
-        <v>17</v>
-      </c>
       <c r="I66" s="7">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="J66" s="7">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="K66" s="4">
-        <v>113.13421</v>
+        <v>75.357900000000001</v>
       </c>
       <c r="L66" s="4">
-        <v>59.772829999999999</v>
+        <v>105.13197</v>
       </c>
       <c r="M66" s="4">
-        <v>0</v>
+        <v>130.32283666666669</v>
       </c>
       <c r="N66" s="4">
-        <v>-59.772829999999999</v>
+        <v>51.255434000000037</v>
       </c>
       <c r="O66" s="5">
         <v>0</v>
@@ -4331,52 +4381,52 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
-        <v>2023303</v>
+        <v>2011731</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="C67" s="9">
-        <v>201624800522</v>
+        <v>201173100172</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F67" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G67" s="3">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H67" s="3">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I67" s="7">
-        <v>16.666666666666671</v>
+        <v>19</v>
       </c>
       <c r="J67" s="7">
-        <v>0.6666666666666714</v>
+        <v>23</v>
       </c>
       <c r="K67" s="4">
-        <v>26.563960000000002</v>
+        <v>29.148759999999999</v>
       </c>
       <c r="L67" s="4">
-        <v>127.87345000000001</v>
+        <v>39.288800000000002</v>
       </c>
       <c r="M67" s="4">
-        <v>0</v>
+        <v>19.30109666666667</v>
       </c>
       <c r="N67" s="4">
-        <v>-127.87345000000001</v>
+        <v>-16.127483999999999</v>
       </c>
       <c r="O67" s="5">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="P67" s="5">
-        <v>0</v>
+        <v>0.39288800000000001</v>
       </c>
       <c r="Q67" s="6">
         <v>250</v>
@@ -4385,182 +4435,214 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
-        <v>2023085</v>
+        <v>2002060</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C68" s="9">
-        <v>201636400069</v>
+        <v>200206000047</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="F68" s="3">
+        <v>16</v>
+      </c>
+      <c r="G68" s="3">
+        <v>14</v>
+      </c>
+      <c r="H68" s="3">
+        <v>13</v>
+      </c>
+      <c r="I68" s="7">
+        <v>14.66666666666667</v>
+      </c>
+      <c r="J68" s="7">
+        <v>21.666666666666671</v>
+      </c>
+      <c r="K68" s="4">
+        <v>132.00389999999999</v>
+      </c>
+      <c r="L68" s="4">
+        <v>176.67819</v>
+      </c>
+      <c r="M68" s="4">
+        <v>162.89900333333341</v>
+      </c>
+      <c r="N68" s="4">
+        <v>18.800614000000081</v>
+      </c>
+      <c r="O68" s="5">
+        <v>0</v>
+      </c>
+      <c r="P68" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>0</v>
+      </c>
+      <c r="R68" s="8"/>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
+        <v>2018993</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G68" s="3">
+      <c r="C69" s="9">
+        <v>201613300250</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H68" s="3">
+      <c r="F69" s="3">
         <v>22</v>
       </c>
-      <c r="I68" s="7">
-        <v>43.333333333333343</v>
-      </c>
-      <c r="J68" s="7">
-        <v>41.333333333333343</v>
-      </c>
-      <c r="K68" s="4">
-        <v>87.600129999999993</v>
-      </c>
-      <c r="L68" s="4">
-        <v>71.982050000000001</v>
-      </c>
-      <c r="M68" s="4">
-        <v>81.972930000000005</v>
-      </c>
-      <c r="N68" s="4">
-        <v>26.385466000000012</v>
-      </c>
-      <c r="O68" s="5">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="6">
-        <v>0</v>
-      </c>
-      <c r="R68" s="8"/>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="9">
-        <v>201740900008</v>
-      </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="3">
-        <v>0</v>
-      </c>
       <c r="G69" s="3">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H69" s="3">
-        <v>36</v>
-      </c>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="I69" s="7">
+        <v>30.333333333333329</v>
+      </c>
+      <c r="J69" s="7">
+        <v>24.333333333333329</v>
+      </c>
       <c r="K69" s="4">
-        <v>0</v>
+        <v>36.459760000000003</v>
       </c>
       <c r="L69" s="4">
-        <v>169.58651</v>
-      </c>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
+        <v>58.332389999999997</v>
+      </c>
+      <c r="M69" s="4">
+        <v>31.68701333333334</v>
+      </c>
+      <c r="N69" s="4">
+        <v>-20.307973999999991</v>
+      </c>
       <c r="O69" s="5">
         <v>0</v>
       </c>
       <c r="P69" s="5">
-        <v>0</v>
+        <v>0.58332390000000001</v>
       </c>
       <c r="Q69" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R69" s="8"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
+      <c r="A70" s="2">
+        <v>2002070</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C70" s="9">
-        <v>201744800627</v>
-      </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+        <v>200207000230</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H70" s="3">
-        <v>4</v>
-      </c>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="I70" s="7">
+        <v>11</v>
+      </c>
+      <c r="J70" s="7">
+        <v>11</v>
+      </c>
       <c r="K70" s="4">
         <v>0</v>
       </c>
       <c r="L70" s="4">
-        <v>8.9114599999999999</v>
-      </c>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
+        <v>782.71015</v>
+      </c>
+      <c r="M70" s="4">
+        <v>283.22349333333341</v>
+      </c>
+      <c r="N70" s="4">
+        <v>-442.84195799999992</v>
+      </c>
       <c r="O70" s="5">
         <v>0</v>
       </c>
       <c r="P70" s="5">
-        <v>0</v>
+        <v>7.8271015000000004</v>
       </c>
       <c r="Q70" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R70" s="8"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
-        <v>2022939</v>
+        <v>2002060</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C71" s="9">
-        <v>201899300053</v>
+        <v>200206000101</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F71" s="3">
+        <v>18</v>
+      </c>
+      <c r="G71" s="3">
+        <v>32</v>
+      </c>
+      <c r="H71" s="3">
         <v>26</v>
       </c>
-      <c r="G71" s="3">
-        <v>27</v>
-      </c>
-      <c r="H71" s="3">
-        <v>19</v>
-      </c>
       <c r="I71" s="7">
-        <v>24.333333333333329</v>
+        <v>24.666666666666671</v>
       </c>
       <c r="J71" s="7">
-        <v>25.333333333333329</v>
+        <v>18.666666666666671</v>
       </c>
       <c r="K71" s="4">
-        <v>43.482939999999999</v>
+        <v>47.029890000000002</v>
       </c>
       <c r="L71" s="4">
-        <v>55.590969999999999</v>
+        <v>132.23799</v>
       </c>
       <c r="M71" s="4">
-        <v>37.893526666666673</v>
+        <v>92.999686666666662</v>
       </c>
       <c r="N71" s="4">
-        <v>-10.11873799999999</v>
+        <v>-20.638366000000001</v>
       </c>
       <c r="O71" s="5">
         <v>0</v>
       </c>
       <c r="P71" s="5">
-        <v>0.55590969999999995</v>
+        <v>1.3223799000000001</v>
       </c>
       <c r="Q71" s="6">
         <v>250</v>
@@ -4569,52 +4651,52 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
-        <v>2022939</v>
+        <v>2023085</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C72" s="9">
-        <v>201899300223</v>
+        <v>201063400142</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F72" s="3">
+        <v>32</v>
+      </c>
+      <c r="G72" s="3">
         <v>30</v>
       </c>
-      <c r="F72" s="3">
-        <v>18</v>
-      </c>
-      <c r="G72" s="3">
-        <v>20</v>
-      </c>
       <c r="H72" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I72" s="7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J72" s="7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K72" s="4">
-        <v>27.107030000000002</v>
+        <v>114.90956</v>
       </c>
       <c r="L72" s="4">
-        <v>33.319200000000002</v>
+        <v>93.199730000000002</v>
       </c>
       <c r="M72" s="4">
-        <v>28.339396666666669</v>
+        <v>78.631203333333346</v>
       </c>
       <c r="N72" s="4">
-        <v>0.68807600000000235</v>
+        <v>1.157714000000013</v>
       </c>
       <c r="O72" s="5">
         <v>0</v>
       </c>
       <c r="P72" s="5">
-        <v>0.24989400000000001</v>
+        <v>0.69899797499999994</v>
       </c>
       <c r="Q72" s="6">
         <v>250</v>
@@ -4629,46 +4711,46 @@
         <v>41</v>
       </c>
       <c r="C73" s="9">
-        <v>201899300414</v>
+        <v>201327000073</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F73" s="3">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G73" s="3">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H73" s="3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I73" s="7">
-        <v>36.666666666666657</v>
+        <v>31.333333333333329</v>
       </c>
       <c r="J73" s="7">
-        <v>27.666666666666661</v>
+        <v>27.333333333333329</v>
       </c>
       <c r="K73" s="4">
-        <v>85.553660000000008</v>
+        <v>68.409880000000001</v>
       </c>
       <c r="L73" s="4">
-        <v>115.84715</v>
+        <v>85.947040000000001</v>
       </c>
       <c r="M73" s="4">
-        <v>86.13788333333332</v>
+        <v>49.752850000000002</v>
       </c>
       <c r="N73" s="4">
-        <v>-12.481690000000009</v>
+        <v>-26.24362</v>
       </c>
       <c r="O73" s="5">
         <v>0</v>
       </c>
       <c r="P73" s="5">
-        <v>1.1584715000000001</v>
+        <v>0.85947040000000008</v>
       </c>
       <c r="Q73" s="6">
         <v>250</v>
@@ -4677,52 +4759,52 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
-        <v>2021125</v>
+        <v>2002060</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="C74" s="9">
-        <v>202112500012</v>
+        <v>200206000046</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F74" s="3">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G74" s="3">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H74" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I74" s="7">
-        <v>17.333333333333329</v>
+        <v>37</v>
       </c>
       <c r="J74" s="7">
-        <v>16.333333333333329</v>
+        <v>34</v>
       </c>
       <c r="K74" s="4">
-        <v>9.4154800000000005</v>
+        <v>191.05100999999999</v>
       </c>
       <c r="L74" s="4">
-        <v>30.034099999999999</v>
+        <v>240.58680000000001</v>
       </c>
       <c r="M74" s="4">
-        <v>4.1351266666666664</v>
+        <v>215.37703666666661</v>
       </c>
       <c r="N74" s="4">
-        <v>-25.071947999999999</v>
+        <v>17.865643999999921</v>
       </c>
       <c r="O74" s="5">
         <v>0</v>
       </c>
       <c r="P74" s="5">
-        <v>0.30034100000000002</v>
+        <v>1.2029339999999999</v>
       </c>
       <c r="Q74" s="6">
         <v>250</v>
@@ -4731,52 +4813,52 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
-        <v>2021330</v>
+        <v>2023002</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C75" s="9">
-        <v>202133000511</v>
+        <v>201074800326</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F75" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G75" s="3">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H75" s="3">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I75" s="7">
-        <v>16.333333333333329</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="J75" s="7">
-        <v>2.333333333333329</v>
+        <v>-22.666666666666671</v>
       </c>
       <c r="K75" s="4">
-        <v>3.39411</v>
+        <v>23.7637</v>
       </c>
       <c r="L75" s="4">
-        <v>123.17138</v>
+        <v>108.67234999999999</v>
       </c>
       <c r="M75" s="4">
-        <v>36.303743333333337</v>
+        <v>16.91567666666667</v>
       </c>
       <c r="N75" s="4">
-        <v>-79.606887999999998</v>
+        <v>-88.373537999999996</v>
       </c>
       <c r="O75" s="5">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="P75" s="5">
-        <v>1.2317138000000001</v>
+        <v>1.0867235</v>
       </c>
       <c r="Q75" s="6">
         <v>500</v>
@@ -4785,46 +4867,46 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
-        <v>2022639</v>
+        <v>2002060</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C76" s="9">
-        <v>202263900079</v>
+        <v>200206000044</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F76" s="3">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G76" s="3">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H76" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I76" s="7">
-        <v>41.666666666666657</v>
+        <v>24.666666666666671</v>
       </c>
       <c r="J76" s="7">
-        <v>34.666666666666657</v>
+        <v>24.666666666666671</v>
       </c>
       <c r="K76" s="4">
-        <v>117.75586</v>
+        <v>131.09913</v>
       </c>
       <c r="L76" s="4">
-        <v>114.47995</v>
+        <v>79.851129999999998</v>
       </c>
       <c r="M76" s="4">
-        <v>0</v>
+        <v>94.131806666666662</v>
       </c>
       <c r="N76" s="4">
-        <v>-114.47995</v>
+        <v>33.107037999999989</v>
       </c>
       <c r="O76" s="5">
         <v>0</v>
@@ -4839,52 +4921,52 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
-        <v>2022939</v>
+        <v>2018993</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C77" s="9">
-        <v>202293900019</v>
+        <v>201178500087</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F77" s="3">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G77" s="3">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H77" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I77" s="7">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="J77" s="7">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="K77" s="4">
-        <v>109.84516000000001</v>
+        <v>62.757689999999997</v>
       </c>
       <c r="L77" s="4">
-        <v>66.066460000000006</v>
+        <v>67.887879999999996</v>
       </c>
       <c r="M77" s="4">
-        <v>53.717599999999997</v>
+        <v>58.533586666666672</v>
       </c>
       <c r="N77" s="4">
-        <v>-1.605340000000012</v>
+        <v>2.3524240000000129</v>
       </c>
       <c r="O77" s="5">
         <v>0</v>
       </c>
       <c r="P77" s="5">
-        <v>0.66066460000000005</v>
+        <v>0.50915909999999998</v>
       </c>
       <c r="Q77" s="6">
         <v>250</v>
@@ -4893,52 +4975,52 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
-        <v>2022939</v>
+        <v>2009842</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C78" s="9">
-        <v>202293900020</v>
+        <v>200984200845</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F78" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G78" s="3">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="H78" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I78" s="7">
-        <v>24.333333333333329</v>
+        <v>20</v>
       </c>
       <c r="J78" s="7">
-        <v>30.333333333333329</v>
+        <v>19</v>
       </c>
       <c r="K78" s="4">
-        <v>46.2059</v>
+        <v>8.8895699999999991</v>
       </c>
       <c r="L78" s="4">
-        <v>31.27309</v>
+        <v>63.370780000000003</v>
       </c>
       <c r="M78" s="4">
-        <v>28.102313333333331</v>
+        <v>18.51793</v>
       </c>
       <c r="N78" s="4">
-        <v>2.4496859999999958</v>
+        <v>-41.149264000000002</v>
       </c>
       <c r="O78" s="5">
         <v>0</v>
       </c>
       <c r="P78" s="5">
-        <v>0.15636544999999999</v>
+        <v>0.63370779999999993</v>
       </c>
       <c r="Q78" s="6">
         <v>250</v>
@@ -4946,53 +5028,45 @@
       <c r="R78" s="8"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A79" s="2">
-        <v>2023085</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>59</v>
-      </c>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
       <c r="C79" s="9">
-        <v>202308500082</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>200210502407</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
       <c r="F79" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G79" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H79" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I79" s="7">
-        <v>15.66666666666667</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="J79" s="7">
-        <v>13.66666666666667</v>
+        <v>3.6666666666666679</v>
       </c>
       <c r="K79" s="4">
-        <v>24.048690000000001</v>
+        <v>28.37181</v>
       </c>
       <c r="L79" s="4">
-        <v>35.72383</v>
+        <v>53.864150000000002</v>
       </c>
       <c r="M79" s="4">
-        <v>22.844533333333331</v>
+        <v>0</v>
       </c>
       <c r="N79" s="4">
-        <v>-8.3103900000000017</v>
+        <v>-53.864150000000002</v>
       </c>
       <c r="O79" s="5">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="P79" s="5">
-        <v>0.35723830000000001</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="6">
         <v>250</v>
@@ -5000,210 +5074,154 @@
       <c r="R79" s="8"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A80" s="2">
-        <v>2023177</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
       <c r="C80" s="9">
-        <v>202317700011</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>200210502426</v>
+      </c>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
       <c r="F80" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G80" s="3">
+        <v>23</v>
+      </c>
+      <c r="H80" s="3">
+        <v>15</v>
+      </c>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="4">
+        <v>0</v>
+      </c>
+      <c r="L80" s="4">
+        <v>65.215410000000006</v>
+      </c>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="5">
+        <v>0</v>
+      </c>
+      <c r="P80" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>0</v>
+      </c>
+      <c r="R80" s="8"/>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="9">
+        <v>200848700017</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>22</v>
+      </c>
+      <c r="H81" s="3">
+        <v>9</v>
+      </c>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="4">
+        <v>0</v>
+      </c>
+      <c r="L81" s="4">
+        <v>24.178380000000001</v>
+      </c>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="5">
+        <v>0</v>
+      </c>
+      <c r="P81" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>0</v>
+      </c>
+      <c r="R81" s="8"/>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="9">
+        <v>201624800468</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="3">
+        <v>33</v>
+      </c>
+      <c r="G82" s="3">
+        <v>32</v>
+      </c>
+      <c r="H82" s="3">
         <v>17</v>
       </c>
-      <c r="H80" s="3">
-        <v>10</v>
-      </c>
-      <c r="I80" s="7">
-        <v>18</v>
-      </c>
-      <c r="J80" s="7">
-        <v>28</v>
-      </c>
-      <c r="K80" s="4">
-        <v>33.348080000000003</v>
-      </c>
-      <c r="L80" s="4">
-        <v>20.83699</v>
-      </c>
-      <c r="M80" s="4">
-        <v>24.544803333333331</v>
-      </c>
-      <c r="N80" s="4">
-        <v>8.6167739999999959</v>
-      </c>
-      <c r="O80" s="5">
-        <v>0</v>
-      </c>
-      <c r="P80" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="6">
-        <v>0</v>
-      </c>
-      <c r="R80" s="8"/>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A81" s="2">
-        <v>2023177</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C81" s="9">
-        <v>202317700022</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F81" s="3">
-        <v>24</v>
-      </c>
-      <c r="G81" s="3">
-        <v>16</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I82" s="7">
         <v>11</v>
       </c>
-      <c r="I81" s="7">
-        <v>22</v>
-      </c>
-      <c r="J81" s="7">
-        <v>31</v>
-      </c>
-      <c r="K81" s="4">
-        <v>36.343389999999999</v>
-      </c>
-      <c r="L81" s="4">
-        <v>28.312449999999998</v>
-      </c>
-      <c r="M81" s="4">
-        <v>24.969480000000001</v>
-      </c>
-      <c r="N81" s="4">
-        <v>1.6509260000000019</v>
-      </c>
-      <c r="O81" s="5">
-        <v>0</v>
-      </c>
-      <c r="P81" s="5">
-        <v>0.14156225</v>
-      </c>
-      <c r="Q81" s="6">
-        <v>250</v>
-      </c>
-      <c r="R81" s="8"/>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A82" s="2">
-        <v>2023177</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C82" s="9">
-        <v>202317700044</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F82" s="3">
-        <v>24</v>
-      </c>
-      <c r="G82" s="3">
-        <v>25</v>
-      </c>
-      <c r="H82" s="3">
-        <v>19</v>
-      </c>
-      <c r="I82" s="7">
-        <v>25</v>
-      </c>
       <c r="J82" s="7">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K82" s="4">
-        <v>44.575009999999999</v>
+        <v>113.13421</v>
       </c>
       <c r="L82" s="4">
-        <v>65.395139999999998</v>
+        <v>59.772829999999999</v>
       </c>
       <c r="M82" s="4">
-        <v>48.297863333333332</v>
+        <v>0</v>
       </c>
       <c r="N82" s="4">
-        <v>-7.4377040000000036</v>
+        <v>-59.772829999999999</v>
       </c>
       <c r="O82" s="5">
         <v>0</v>
       </c>
       <c r="P82" s="5">
-        <v>0.65395139999999996</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="6">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R82" s="8"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A83" s="2">
-        <v>2023177</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
       <c r="C83" s="9">
-        <v>202317700120</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>201740900008</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
       <c r="F83" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H83" s="3">
-        <v>16</v>
-      </c>
-      <c r="I83" s="7">
-        <v>28.333333333333329</v>
-      </c>
-      <c r="J83" s="7">
-        <v>32.333333333333329</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
       <c r="K83" s="4">
-        <v>74.071690000000004</v>
+        <v>0</v>
       </c>
       <c r="L83" s="4">
-        <v>62.208060000000003</v>
-      </c>
-      <c r="M83" s="4">
-        <v>66.375219999999999</v>
-      </c>
-      <c r="N83" s="4">
-        <v>17.44220399999999</v>
-      </c>
+        <v>169.58651</v>
+      </c>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
       <c r="O83" s="5">
         <v>0</v>
       </c>
@@ -5216,48 +5234,32 @@
       <c r="R83" s="8"/>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A84" s="2">
-        <v>2023177</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
       <c r="C84" s="9">
-        <v>202317700141</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>201744800627</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
       <c r="F84" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G84" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H84" s="3">
-        <v>11</v>
-      </c>
-      <c r="I84" s="7">
-        <v>24.333333333333329</v>
-      </c>
-      <c r="J84" s="7">
-        <v>33.333333333333329</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
       <c r="K84" s="4">
-        <v>20.782160000000001</v>
+        <v>0</v>
       </c>
       <c r="L84" s="4">
-        <v>29.47757</v>
-      </c>
-      <c r="M84" s="4">
-        <v>41.320500000000003</v>
-      </c>
-      <c r="N84" s="4">
-        <v>20.107030000000002</v>
-      </c>
+        <v>8.9114599999999999</v>
+      </c>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
       <c r="O84" s="5">
         <v>0</v>
       </c>
@@ -5422,6 +5424,9 @@
       <c r="R88" s="8"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q88">
+    <sortCondition ref="D2:D88"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Dashboard_Backend.xlsx
+++ b/Dashboard_Backend.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -95,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +109,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -480,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -492,14 +497,15 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -570,20 +576,25 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>% TO Achievement</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>TO Remaining Target</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Range Selling Reward</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>T.O. Reward</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>WDSM Claim</t>
         </is>
@@ -635,16 +646,19 @@
       <c r="M2" s="4" t="n">
         <v>41.80709333333333</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="5" t="n">
+        <v>99.95987921666884</v>
+      </c>
+      <c r="O2" s="4" t="n">
         <v>8.378191999999991</v>
       </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
+      <c r="P2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -694,16 +708,19 @@
       <c r="M3" s="4" t="n">
         <v>28.76989666666667</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="5" t="n">
+        <v>97.36051653064678</v>
+      </c>
+      <c r="O3" s="4" t="n">
         <v>6.513356000000002</v>
       </c>
-      <c r="O3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5" t="n">
+      <c r="P3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -753,16 +770,19 @@
       <c r="M4" s="4" t="n">
         <v>27.05408666666667</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="5" t="n">
+        <v>64.66028668989749</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>14.971654</v>
       </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
+      <c r="P4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -812,16 +832,19 @@
       <c r="M5" s="4" t="n">
         <v>101.9920266666667</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="5" t="n">
+        <v>147.3006027137807</v>
+      </c>
+      <c r="O5" s="4" t="n">
         <v>-27.84443799999997</v>
       </c>
-      <c r="O5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="5" t="n">
+      <c r="P5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6" t="n">
         <v>1.5023487</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="R5" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -871,16 +894,19 @@
       <c r="M6" s="4" t="n">
         <v>38.77142</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="5" t="n">
+        <v>27.4644570665712</v>
+      </c>
+      <c r="O6" s="4" t="n">
         <v>35.87734399999999</v>
       </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
+      <c r="P6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -924,16 +950,19 @@
       <c r="M7" s="4" t="n">
         <v>9.672739999999999</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="5" t="n">
+        <v>195.422910157825</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>-7.295462000000002</v>
       </c>
-      <c r="O7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="5" t="n">
+      <c r="P7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6" t="n">
         <v>0.1890275</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="R7" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -983,16 +1012,19 @@
       <c r="M8" s="4" t="n">
         <v>55.74277666666666</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="5" t="n">
+        <v>143.2819726179171</v>
+      </c>
+      <c r="O8" s="4" t="n">
         <v>-12.97801800000001</v>
       </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
+      <c r="P8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6" t="n">
         <v>0.7986934999999999</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="R8" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1042,16 +1074,19 @@
       <c r="M9" s="4" t="n">
         <v>31.40123333333334</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="5" t="n">
+        <v>66.35869928675837</v>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>16.84403000000001</v>
       </c>
-      <c r="O9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="5" t="n">
+      <c r="P9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1101,16 +1136,19 @@
       <c r="M10" s="4" t="n">
         <v>345.4742133333334</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="5" t="n">
+        <v>138.0739608312686</v>
+      </c>
+      <c r="O10" s="4" t="n">
         <v>-62.44087399999989</v>
       </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
+      <c r="P10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6" t="n">
         <v>4.7700993</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="R10" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1160,16 +1198,19 @@
       <c r="M11" s="4" t="n">
         <v>93.09971666666667</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="5" t="n">
+        <v>152.2744269003325</v>
+      </c>
+      <c r="O11" s="4" t="n">
         <v>-30.04740000000002</v>
       </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="n">
+      <c r="P11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6" t="n">
         <v>1.4176706</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="R11" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1219,16 +1260,19 @@
       <c r="M12" s="4" t="n">
         <v>200.62471</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="5" t="n">
+        <v>113.2272091508569</v>
+      </c>
+      <c r="O12" s="4" t="n">
         <v>13.58789199999998</v>
       </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
+      <c r="P12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6" t="n">
         <v>1.1358088</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="R12" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1278,16 +1322,19 @@
       <c r="M13" s="4" t="n">
         <v>171.3441033333334</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="5" t="n">
+        <v>118.3081098540284</v>
+      </c>
+      <c r="O13" s="4" t="n">
         <v>2.89895400000006</v>
       </c>
-      <c r="O13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5" t="n">
+      <c r="P13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="6" t="n">
         <v>1.520354775</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="R13" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1337,16 +1384,19 @@
       <c r="M14" s="4" t="n">
         <v>181.2304066666667</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="5" t="n">
+        <v>70.61674271657355</v>
+      </c>
+      <c r="O14" s="4" t="n">
         <v>89.49747800000004</v>
       </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
+      <c r="P14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1396,16 +1446,19 @@
       <c r="M15" s="4" t="n">
         <v>58.09981666666666</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="5" t="n">
+        <v>101.5342446576854</v>
+      </c>
+      <c r="O15" s="4" t="n">
         <v>10.72856999999998</v>
       </c>
-      <c r="O15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="5" t="n">
+      <c r="P15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1455,16 +1508,19 @@
       <c r="M16" s="4" t="n">
         <v>122.7412966666667</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="5" t="n">
+        <v>60.54648436851829</v>
+      </c>
+      <c r="O16" s="4" t="n">
         <v>72.97401600000003</v>
       </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
+      <c r="P16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1514,16 +1570,19 @@
       <c r="M17" s="4" t="n">
         <v>66.66565333333334</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="5" t="n">
+        <v>164.4620648233853</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>-29.64092599999999</v>
       </c>
-      <c r="O17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="5" t="n">
+      <c r="P17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6" t="n">
         <v>1.0963971</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="R17" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1573,16 +1632,19 @@
       <c r="M18" s="4" t="n">
         <v>133.8716033333334</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="5" t="n">
+        <v>57.66070479323206</v>
+      </c>
+      <c r="O18" s="4" t="n">
         <v>83.45461400000009</v>
       </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
+      <c r="P18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1632,16 +1694,19 @@
       <c r="M19" s="4" t="n">
         <v>68.79257333333332</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="5" t="n">
+        <v>59.93196358599175</v>
+      </c>
+      <c r="O19" s="4" t="n">
         <v>41.32234799999998</v>
       </c>
-      <c r="O19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5" t="n">
+      <c r="P19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1691,16 +1756,19 @@
       <c r="M20" s="4" t="n">
         <v>663.5676500000001</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="5" t="n">
+        <v>112.5976469769133</v>
+      </c>
+      <c r="O20" s="4" t="n">
         <v>49.11962000000017</v>
       </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="n">
+      <c r="P20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6" t="n">
         <v>3.735807799999999</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="R20" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1750,16 +1818,19 @@
       <c r="M21" s="4" t="n">
         <v>52.05216333333333</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="5" t="n">
+        <v>64.98855731196315</v>
+      </c>
+      <c r="O21" s="4" t="n">
         <v>28.634646</v>
       </c>
-      <c r="O21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="5" t="n">
+      <c r="P21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1809,16 +1880,19 @@
       <c r="M22" s="4" t="n">
         <v>111.7789166666667</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="5" t="n">
+        <v>39.40358460562403</v>
+      </c>
+      <c r="O22" s="4" t="n">
         <v>90.08980000000004</v>
       </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
+      <c r="P22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1868,16 +1942,19 @@
       <c r="M23" s="4" t="n">
         <v>70.16096333333333</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="5" t="n">
+        <v>122.9601417958486</v>
+      </c>
+      <c r="O23" s="4" t="n">
         <v>-2.076864000000015</v>
       </c>
-      <c r="O23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="5" t="n">
+      <c r="P23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6" t="n">
         <v>0.8627002</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="R23" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1927,16 +2004,19 @@
       <c r="M24" s="4" t="n">
         <v>76.35146999999999</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4" t="n">
         <v>91.62176399999998</v>
       </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
+      <c r="P24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1986,16 +2066,19 @@
       <c r="M25" s="4" t="n">
         <v>29.14807333333333</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="5" t="n">
+        <v>129.8645696650962</v>
+      </c>
+      <c r="O25" s="4" t="n">
         <v>-2.875332000000007</v>
       </c>
-      <c r="O25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="5" t="n">
+      <c r="P25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6" t="n">
         <v>0.3785302</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="R25" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2045,16 +2128,19 @@
       <c r="M26" s="4" t="n">
         <v>47.29138666666666</v>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="5" t="n">
+        <v>79.44863250644092</v>
+      </c>
+      <c r="O26" s="4" t="n">
         <v>19.17730399999999</v>
       </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
+      <c r="P26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2104,16 +2190,19 @@
       <c r="M27" s="4" t="n">
         <v>25.95256666666667</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="5" t="n">
+        <v>49.56831501572741</v>
+      </c>
+      <c r="O27" s="4" t="n">
         <v>18.27883</v>
       </c>
-      <c r="O27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="5" t="n">
+      <c r="P27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2163,16 +2252,19 @@
       <c r="M28" s="4" t="n">
         <v>34.00460333333334</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="5" t="n">
+        <v>199.3953857815917</v>
+      </c>
+      <c r="O28" s="4" t="n">
         <v>-26.99808599999999</v>
       </c>
-      <c r="O28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="5" t="n">
+      <c r="P28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="6" t="n">
         <v>0.6780361</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="R28" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2222,16 +2314,19 @@
       <c r="M29" s="4" t="n">
         <v>52.10580000000001</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="5" t="n">
+        <v>116.0138794529592</v>
+      </c>
+      <c r="O29" s="4" t="n">
         <v>2.077000000000012</v>
       </c>
-      <c r="O29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="5" t="n">
+      <c r="P29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="6" t="n">
         <v>0.4533747</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="R29" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2281,16 +2376,19 @@
       <c r="M30" s="4" t="n">
         <v>52.83083666666666</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="5" t="n">
+        <v>205.8755016246509</v>
+      </c>
+      <c r="O30" s="4" t="n">
         <v>-45.368746</v>
       </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
+      <c r="P30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="6" t="n">
         <v>1.0876575</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="R30" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2334,16 +2432,19 @@
       <c r="M31" s="4" t="n">
         <v/>
       </c>
-      <c r="N31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="5" t="n">
+      <c r="N31" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v/>
+      </c>
+      <c r="P31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2387,16 +2488,19 @@
       <c r="M32" s="4" t="n">
         <v/>
       </c>
-      <c r="N32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
+      <c r="N32" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v/>
+      </c>
+      <c r="P32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,16 +2550,19 @@
       <c r="M33" s="4" t="n">
         <v>98.51073333333333</v>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="5" t="n">
+        <v>136.9360631430348</v>
+      </c>
+      <c r="O33" s="4" t="n">
         <v>-16.68383999999999</v>
       </c>
-      <c r="O33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="5" t="n">
+      <c r="P33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="6" t="n">
         <v>1.3489672</v>
       </c>
-      <c r="Q33" s="6" t="n">
+      <c r="R33" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2505,16 +2612,19 @@
       <c r="M34" s="4" t="n">
         <v>208.18544</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="5" t="n">
+        <v>67.16479788404031</v>
+      </c>
+      <c r="O34" s="4" t="n">
         <v>109.995198</v>
       </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
+      <c r="P34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2564,16 +2674,19 @@
       <c r="M35" s="4" t="n">
         <v>107.8869266666667</v>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="5" t="n">
+        <v>56.12880250736587</v>
+      </c>
+      <c r="O35" s="4" t="n">
         <v>68.90867200000004</v>
       </c>
-      <c r="O35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="5" t="n">
+      <c r="P35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2623,16 +2736,19 @@
       <c r="M36" s="4" t="n">
         <v>91.87452999999999</v>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="5" t="n">
+        <v>17.77533991194295</v>
+      </c>
+      <c r="O36" s="4" t="n">
         <v>93.91842599999998</v>
       </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="5" t="n">
+      <c r="P36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2682,16 +2798,19 @@
       <c r="M37" s="4" t="n">
         <v>65.54083333333334</v>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="5" t="n">
+        <v>203.7675800073745</v>
+      </c>
+      <c r="O37" s="4" t="n">
         <v>-54.90197000000001</v>
       </c>
-      <c r="O37" s="5" t="n">
+      <c r="P37" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="P37" s="5" t="n">
+      <c r="Q37" s="6" t="n">
         <v>1.3355097</v>
       </c>
-      <c r="Q37" s="6" t="n">
+      <c r="R37" s="7" t="n">
         <v>500</v>
       </c>
     </row>
@@ -2741,16 +2860,19 @@
       <c r="M38" s="4" t="n">
         <v>35.51502</v>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="5" t="n">
+        <v>141.4664274439378</v>
+      </c>
+      <c r="O38" s="4" t="n">
         <v>-7.623806000000002</v>
       </c>
-      <c r="O38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="5" t="n">
+      <c r="P38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="6" t="n">
         <v>0.5024183</v>
       </c>
-      <c r="Q38" s="6" t="n">
+      <c r="R38" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2800,16 +2922,19 @@
       <c r="M39" s="4" t="n">
         <v>29.01681666666667</v>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="5" t="n">
+        <v>66.78885634709526</v>
+      </c>
+      <c r="O39" s="4" t="n">
         <v>15.44018</v>
       </c>
-      <c r="O39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="5" t="n">
+      <c r="P39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2853,16 +2978,19 @@
       <c r="M40" s="4" t="n">
         <v/>
       </c>
-      <c r="N40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
+      <c r="N40" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v/>
+      </c>
+      <c r="P40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2912,16 +3040,19 @@
       <c r="M41" s="4" t="n">
         <v>316.9292133333333</v>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4" t="n">
         <v>380.3150559999999</v>
       </c>
-      <c r="O41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="5" t="n">
+      <c r="P41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2971,16 +3102,19 @@
       <c r="M42" s="4" t="n">
         <v>40.93277333333334</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="5" t="n">
+        <v>183.169484729107</v>
+      </c>
+      <c r="O42" s="4" t="n">
         <v>-25.85702199999999</v>
       </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="5" t="n">
+      <c r="P42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="6" t="n">
         <v>0.7497635</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="R42" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -3030,16 +3164,19 @@
       <c r="M43" s="4" t="n">
         <v>34.67592666666667</v>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="5" t="n">
+        <v>133.5102604323576</v>
+      </c>
+      <c r="O43" s="4" t="n">
         <v>-4.684808000000004</v>
       </c>
-      <c r="O43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="5" t="n">
+      <c r="P43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="6" t="n">
         <v>0.4629592</v>
       </c>
-      <c r="Q43" s="6" t="n">
+      <c r="R43" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -3089,16 +3226,19 @@
       <c r="M44" s="4" t="n">
         <v>35.94880333333333</v>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="5" t="n">
+        <v>97.95619529662602</v>
+      </c>
+      <c r="O44" s="4" t="n">
         <v>7.924483999999993</v>
       </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="5" t="n">
+      <c r="P44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3148,16 +3288,19 @@
       <c r="M45" s="4" t="n">
         <v>92.34347000000001</v>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="5" t="n">
+        <v>92.89771112131696</v>
+      </c>
+      <c r="O45" s="4" t="n">
         <v>25.02719400000001</v>
       </c>
-      <c r="O45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="5" t="n">
+      <c r="P45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3207,16 +3350,19 @@
       <c r="M46" s="4" t="n">
         <v>102.4090866666667</v>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="5" t="n">
+        <v>46.68912843215799</v>
+      </c>
+      <c r="O46" s="4" t="n">
         <v>75.07699400000004</v>
       </c>
-      <c r="O46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="5" t="n">
+      <c r="P46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3266,16 +3412,19 @@
       <c r="M47" s="4" t="n">
         <v>30.98505666666667</v>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="5" t="n">
+        <v>84.7751878674419</v>
+      </c>
+      <c r="O47" s="4" t="n">
         <v>10.914428</v>
       </c>
-      <c r="O47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="5" t="n">
+      <c r="P47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3325,16 +3474,19 @@
       <c r="M48" s="4" t="n">
         <v>56.46564333333333</v>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="5" t="n">
+        <v>5.500158710078158</v>
+      </c>
+      <c r="O48" s="4" t="n">
         <v>64.65307199999999</v>
       </c>
-      <c r="O48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="5" t="n">
+      <c r="P48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3384,16 +3536,19 @@
       <c r="M49" s="4" t="n">
         <v>75.18834</v>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4" t="n">
         <v>90.22600799999999</v>
       </c>
-      <c r="O49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="5" t="n">
+      <c r="P49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3443,16 +3598,19 @@
       <c r="M50" s="4" t="n">
         <v>140.0387133333333</v>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="5" t="n">
+        <v>57.7054644936993</v>
+      </c>
+      <c r="O50" s="4" t="n">
         <v>87.23646599999995</v>
       </c>
-      <c r="O50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="5" t="n">
+      <c r="P50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3502,16 +3660,19 @@
       <c r="M51" s="4" t="n">
         <v>203.3141666666667</v>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="5" t="n">
+        <v>57.81887800899263</v>
+      </c>
+      <c r="O51" s="4" t="n">
         <v>126.42303</v>
       </c>
-      <c r="O51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="5" t="n">
+      <c r="P51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3561,16 +3722,19 @@
       <c r="M52" s="4" t="n">
         <v>53.99136000000001</v>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="5" t="n">
+        <v>102.2609543452878</v>
+      </c>
+      <c r="O52" s="4" t="n">
         <v>9.577552000000011</v>
       </c>
-      <c r="O52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="5" t="n">
+      <c r="P52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3620,16 +3784,19 @@
       <c r="M53" s="4" t="n">
         <v>122.0849566666667</v>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="5" t="n">
+        <v>52.05278499095451</v>
+      </c>
+      <c r="O53" s="4" t="n">
         <v>82.95332800000003</v>
       </c>
-      <c r="O53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="5" t="n">
+      <c r="P53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3679,16 +3846,19 @@
       <c r="M54" s="4" t="n">
         <v>96.27256333333332</v>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N54" s="5" t="n">
+        <v>95.00231097340333</v>
+      </c>
+      <c r="O54" s="4" t="n">
         <v>24.06591599999999</v>
       </c>
-      <c r="O54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="5" t="n">
+      <c r="P54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3738,16 +3908,19 @@
       <c r="M55" s="4" t="n">
         <v>144.5002333333333</v>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="5" t="n">
+        <v>40.71756746874919</v>
+      </c>
+      <c r="O55" s="4" t="n">
         <v>114.5633</v>
       </c>
-      <c r="O55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="5" t="n">
+      <c r="P55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3797,16 +3970,19 @@
       <c r="M56" s="4" t="n">
         <v>92.42781000000001</v>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N56" s="5" t="n">
+        <v>45.2250680828638</v>
+      </c>
+      <c r="O56" s="4" t="n">
         <v>69.11283200000001</v>
       </c>
-      <c r="O56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5" t="n">
+      <c r="P56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3856,16 +4032,19 @@
       <c r="M57" s="4" t="n">
         <v>119.0924233333333</v>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="5" t="n">
+        <v>68.57819138620268</v>
+      </c>
+      <c r="O57" s="4" t="n">
         <v>61.23947799999995</v>
       </c>
-      <c r="O57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="5" t="n">
+      <c r="P57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3915,16 +4094,19 @@
       <c r="M58" s="4" t="n">
         <v>55.73072666666667</v>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N58" s="5" t="n">
+        <v>138.5564922952736</v>
+      </c>
+      <c r="O58" s="4" t="n">
         <v>-10.341668</v>
       </c>
-      <c r="O58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="5" t="n">
+      <c r="P58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6" t="n">
         <v>0.7721854</v>
       </c>
-      <c r="Q58" s="6" t="n">
+      <c r="R58" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -3974,16 +4156,19 @@
       <c r="M59" s="4" t="n">
         <v>62.44824333333333</v>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="5" t="n">
+        <v>80.95933096169826</v>
+      </c>
+      <c r="O59" s="4" t="n">
         <v>24.38021199999999</v>
       </c>
-      <c r="O59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="5" t="n">
+      <c r="P59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4033,16 +4218,19 @@
       <c r="M60" s="4" t="n">
         <v>117.2941466666667</v>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="N60" s="5" t="n">
+        <v>62.40865557258268</v>
+      </c>
+      <c r="O60" s="4" t="n">
         <v>67.55127600000004</v>
       </c>
-      <c r="O60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="5" t="n">
+      <c r="P60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4092,16 +4280,19 @@
       <c r="M61" s="4" t="n">
         <v>28.85700666666667</v>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="N61" s="5" t="n">
+        <v>239.5590464337835</v>
+      </c>
+      <c r="O61" s="4" t="n">
         <v>-34.501162</v>
       </c>
-      <c r="O61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="5" t="n">
+      <c r="P61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="6" t="n">
         <v>0.6912957000000001</v>
       </c>
-      <c r="Q61" s="6" t="n">
+      <c r="R61" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -4151,16 +4342,19 @@
       <c r="M62" s="4" t="n">
         <v>102.2013766666667</v>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N62" s="5" t="n">
+        <v>34.95523364280839</v>
+      </c>
+      <c r="O62" s="4" t="n">
         <v>86.91692200000003</v>
       </c>
-      <c r="O62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="5" t="n">
+      <c r="P62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4210,16 +4404,19 @@
       <c r="M63" s="4" t="n">
         <v>117.4925266666667</v>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="N63" s="5" t="n">
+        <v>64.86079767115966</v>
+      </c>
+      <c r="O63" s="4" t="n">
         <v>64.78444200000004</v>
       </c>
-      <c r="O63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="5" t="n">
+      <c r="P63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4269,16 +4466,19 @@
       <c r="M64" s="4" t="n">
         <v>38.00519666666667</v>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N64" s="5" t="n">
+        <v>56.61846770253085</v>
+      </c>
+      <c r="O64" s="4" t="n">
         <v>24.088276</v>
       </c>
-      <c r="O64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5" t="n">
+      <c r="P64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4328,16 +4528,19 @@
       <c r="M65" s="4" t="n">
         <v>114.82037</v>
       </c>
-      <c r="N65" s="4" t="n">
+      <c r="N65" s="5" t="n">
+        <v>73.78763890065848</v>
+      </c>
+      <c r="O65" s="4" t="n">
         <v>53.06120399999998</v>
       </c>
-      <c r="O65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="5" t="n">
+      <c r="P65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4387,16 +4590,19 @@
       <c r="M66" s="4" t="n">
         <v>16.55300666666666</v>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="N66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="4" t="n">
         <v>19.86360799999999</v>
       </c>
-      <c r="O66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5" t="n">
+      <c r="P66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4446,16 +4652,19 @@
       <c r="M67" s="4" t="n">
         <v>80.87939</v>
       </c>
-      <c r="N67" s="4" t="n">
+      <c r="N67" s="5" t="n">
+        <v>92.97605978482281</v>
+      </c>
+      <c r="O67" s="4" t="n">
         <v>21.856798</v>
       </c>
-      <c r="O67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="5" t="n">
+      <c r="P67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4505,16 +4714,19 @@
       <c r="M68" s="4" t="n">
         <v>66.39796</v>
       </c>
-      <c r="N68" s="4" t="n">
+      <c r="N68" s="5" t="n">
+        <v>108.8291116172846</v>
+      </c>
+      <c r="O68" s="4" t="n">
         <v>7.417241999999987</v>
       </c>
-      <c r="O68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5" t="n">
+      <c r="P68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4558,16 +4770,19 @@
       <c r="M69" s="4" t="n">
         <v>16.47692</v>
       </c>
-      <c r="N69" s="4" t="n">
+      <c r="N69" s="5" t="n">
+        <v>781.5308322186429</v>
+      </c>
+      <c r="O69" s="4" t="n">
         <v>-108.999906</v>
       </c>
-      <c r="O69" s="5" t="n">
+      <c r="P69" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="P69" s="5" t="n">
+      <c r="Q69" s="6" t="n">
         <v>1.2877221</v>
       </c>
-      <c r="Q69" s="6" t="n">
+      <c r="R69" s="7" t="n">
         <v>500</v>
       </c>
     </row>
@@ -4611,16 +4826,19 @@
       <c r="M70" s="4" t="n">
         <v/>
       </c>
-      <c r="N70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="5" t="n">
+      <c r="N70" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v/>
+      </c>
+      <c r="P70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4670,16 +4888,19 @@
       <c r="M71" s="4" t="n">
         <v>52.21021666666667</v>
       </c>
-      <c r="N71" s="4" t="n">
+      <c r="N71" s="5" t="n">
+        <v>95.22293369784266</v>
+      </c>
+      <c r="O71" s="4" t="n">
         <v>12.93616</v>
       </c>
-      <c r="O71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="5" t="n">
+      <c r="P71" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4729,16 +4950,19 @@
       <c r="M72" s="4" t="n">
         <v>32.73071333333333</v>
       </c>
-      <c r="N72" s="4" t="n">
+      <c r="N72" s="5" t="n">
+        <v>69.84006051808221</v>
+      </c>
+      <c r="O72" s="4" t="n">
         <v>16.41770599999999</v>
       </c>
-      <c r="O72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="5" t="n">
+      <c r="P72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4788,16 +5012,19 @@
       <c r="M73" s="4" t="n">
         <v>95.73931666666665</v>
       </c>
-      <c r="N73" s="4" t="n">
+      <c r="N73" s="5" t="n">
+        <v>77.72855770330513</v>
+      </c>
+      <c r="O73" s="4" t="n">
         <v>40.47038999999998</v>
       </c>
-      <c r="O73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" s="5" t="n">
+      <c r="P73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4847,16 +5074,19 @@
       <c r="M74" s="4" t="n">
         <v>24.53345666666667</v>
       </c>
-      <c r="N74" s="4" t="n">
+      <c r="N74" s="5" t="n">
+        <v>105.912307234325</v>
+      </c>
+      <c r="O74" s="4" t="n">
         <v>3.456198000000001</v>
       </c>
-      <c r="O74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="5" t="n">
+      <c r="P74" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4906,16 +5136,19 @@
       <c r="M75" s="4" t="n">
         <v>75.98127333333333</v>
       </c>
-      <c r="N75" s="4" t="n">
+      <c r="N75" s="5" t="n">
+        <v>145.4865326026387</v>
+      </c>
+      <c r="O75" s="4" t="n">
         <v>-19.364992</v>
       </c>
-      <c r="O75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" s="5" t="n">
+      <c r="P75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="6" t="n">
         <v>1.1054252</v>
       </c>
-      <c r="Q75" s="6" t="n">
+      <c r="R75" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -4965,16 +5198,19 @@
       <c r="M76" s="4" t="n">
         <v>102.3624333333333</v>
       </c>
-      <c r="N76" s="4" t="n">
+      <c r="N76" s="5" t="n">
+        <v>155.1111622004558</v>
+      </c>
+      <c r="O76" s="4" t="n">
         <v>-35.94064000000006</v>
       </c>
-      <c r="O76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="5" t="n">
+      <c r="P76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="6" t="n">
         <v>1.5877556</v>
       </c>
-      <c r="Q76" s="6" t="n">
+      <c r="R76" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -5024,16 +5260,19 @@
       <c r="M77" s="4" t="n">
         <v>82.78822</v>
       </c>
-      <c r="N77" s="4" t="n">
+      <c r="N77" s="5" t="n">
+        <v>60.96124545255353</v>
+      </c>
+      <c r="O77" s="4" t="n">
         <v>48.87713399999999</v>
       </c>
-      <c r="O77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" s="5" t="n">
+      <c r="P77" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5083,16 +5322,19 @@
       <c r="M78" s="4" t="n">
         <v>36.97863</v>
       </c>
-      <c r="N78" s="4" t="n">
+      <c r="N78" s="5" t="n">
+        <v>108.8603607002206</v>
+      </c>
+      <c r="O78" s="4" t="n">
         <v>4.119286000000002</v>
       </c>
-      <c r="O78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="5" t="n">
+      <c r="P78" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5142,16 +5384,19 @@
       <c r="M79" s="4" t="n">
         <v>27.27785333333334</v>
       </c>
-      <c r="N79" s="4" t="n">
+      <c r="N79" s="5" t="n">
+        <v>66.27830929022272</v>
+      </c>
+      <c r="O79" s="4" t="n">
         <v>14.65412400000001</v>
       </c>
-      <c r="O79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="5" t="n">
+      <c r="P79" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5201,16 +5446,19 @@
       <c r="M80" s="4" t="n">
         <v>26.15719333333334</v>
       </c>
-      <c r="N80" s="4" t="n">
+      <c r="N80" s="5" t="n">
+        <v>92.94120240729188</v>
+      </c>
+      <c r="O80" s="4" t="n">
         <v>7.077822000000005</v>
       </c>
-      <c r="O80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="5" t="n">
+      <c r="P80" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5260,16 +5508,19 @@
       <c r="M81" s="4" t="n">
         <v>27.17055</v>
       </c>
-      <c r="N81" s="4" t="n">
+      <c r="N81" s="5" t="n">
+        <v>152.3929769548279</v>
+      </c>
+      <c r="O81" s="4" t="n">
         <v>-8.801350000000006</v>
       </c>
-      <c r="O81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="5" t="n">
+      <c r="P81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="6" t="n">
         <v>0.4140601</v>
       </c>
-      <c r="Q81" s="6" t="n">
+      <c r="R81" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -5319,16 +5570,19 @@
       <c r="M82" s="4" t="n">
         <v>51.07444</v>
       </c>
-      <c r="N82" s="4" t="n">
+      <c r="N82" s="5" t="n">
+        <v>77.26377420878232</v>
+      </c>
+      <c r="O82" s="4" t="n">
         <v>21.827288</v>
       </c>
-      <c r="O82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="5" t="n">
+      <c r="P82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5378,16 +5632,19 @@
       <c r="M83" s="4" t="n">
         <v>67.07551000000001</v>
       </c>
-      <c r="N83" s="4" t="n">
+      <c r="N83" s="5" t="n">
+        <v>91.63939267849025</v>
+      </c>
+      <c r="O83" s="4" t="n">
         <v>19.02302200000001</v>
       </c>
-      <c r="O83" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" s="5" t="n">
+      <c r="P83" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5437,16 +5694,19 @@
       <c r="M84" s="4" t="n">
         <v>45.96094666666666</v>
       </c>
-      <c r="N84" s="4" t="n">
+      <c r="N84" s="5" t="n">
+        <v>115.4427265930989</v>
+      </c>
+      <c r="O84" s="4" t="n">
         <v>2.094565999999986</v>
       </c>
-      <c r="O84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="5" t="n">
+      <c r="P84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="6" t="n">
         <v>0.397939275</v>
       </c>
-      <c r="Q84" s="6" t="n">
+      <c r="R84" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -5496,16 +5756,19 @@
       <c r="M85" s="4" t="n">
         <v>14.04947</v>
       </c>
-      <c r="N85" s="4" t="n">
+      <c r="N85" s="5" t="n">
+        <v>1758.183760668552</v>
+      </c>
+      <c r="O85" s="4" t="n">
         <v>-230.156136</v>
       </c>
-      <c r="O85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" s="5" t="n">
+      <c r="P85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="6" t="n">
         <v>2.470155</v>
       </c>
-      <c r="Q85" s="6" t="n">
+      <c r="R85" s="7" t="n">
         <v>250</v>
       </c>
     </row>
@@ -5549,16 +5812,19 @@
       <c r="M86" s="4" t="n">
         <v/>
       </c>
-      <c r="N86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" s="5" t="n">
+      <c r="N86" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O86" s="4" t="n">
+        <v/>
+      </c>
+      <c r="P86" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5602,16 +5868,19 @@
       <c r="M87" s="4" t="n">
         <v/>
       </c>
-      <c r="N87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="5" t="n">
+      <c r="N87" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O87" s="4" t="n">
+        <v/>
+      </c>
+      <c r="P87" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="7" t="n">
         <v>0</v>
       </c>
     </row>
